--- a/inst/extdata/BS2017SS.xlsx
+++ b/inst/extdata/BS2017SS.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -584,12 +584,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pop_age_transition_index</t>
+          <t>alpha_wt_len</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Integer: age transition matrix (e.g. growth trajectory) index to use deriving length-based predation</t>
+          <t>Alpha parameter from Weight = alpha * Length ^ beta</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sigma_rec_prior</t>
+          <t>beta_wt_len</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Numeric: fixed or initial value of standard deviation for recruitment deviates</t>
+          <t>Beta parameter from Weight = alpha * Length ^ beta</t>
         </is>
       </c>
     </row>
@@ -618,12 +618,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other_food</t>
+          <t>pop_age_transition_index</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Numeric: other food in the ecosystem for each species (kg)</t>
+          <t>Integer: age transition matrix (e.g. growth trajectory) index to use deriving length-based predation</t>
         </is>
       </c>
     </row>
@@ -635,50 +635,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>sigma_rec</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Numeric: fixed or initial value of standard deviation for recruitment deviates</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other_food</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Numeric: other food in the ecosystem for each species (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>estDynamics</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Integer: switch to estimate or fix numbers-at-age: _x000D_
 0 = estimate dynamics_x000D_
 1 = use input numbers-at-age in NbyageFixed, _x000D_
 2 = multiply input numbers-at-age (NbyageFixed) by a single scaling coefficient_x000D_
 3 = multiply input numbers-at-age (NbyageFixed) by age specific scaling coefficient.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>alpha_wt_len</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Alpha parameter from Weight = alpha * Length ^ beta</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>beta_wt_len</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Beta parameter from Weight = alpha * Length ^ beta</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N_sel_bins</t>
+          <t>Selectivity_dimension</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
+          <t>"Age" or "Length".</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sel_curve_pen1</t>
+          <t>N_sel_bins</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
+          <t>Number of age or length bins to estimate non-parametric selectivity for Selectivity = 2 &amp; 5. Not used otherwise</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sel_curve_pen2</t>
+          <t>Sel_curve_pen1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 1st penalty on selectivity.</t>
         </is>
       </c>
     </row>
@@ -867,10 +867,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Sel_curve_pen2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>If selectivity is set to type = 2 or 7 (non-parametric) this value will be the 2nd penalty on selectivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sel_curve_pen3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Deviation-magnitude penalty weight (Sel_curve_pen3) for non-parametric / LogisticPM selectivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Time_varying_sel</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Wether a time-varying selectivity should be estimated for logistic, double logistic selectivity,  descending logistic , or non-parametric (Selectivity = 5). _x000D_
 0 = no_x000D_
@@ -881,40 +915,6 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Time_varying_sel_sd_prior</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>fleet_control</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bin_first_selected</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Age/length bin at which selectivity becomes non-zero</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -923,10 +923,214 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sel_norm_bin1</t>
+          <t>Time_varying_sel_sd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
+        <is>
+          <t>The fixed or initial sd to use for time varying selectivity if set to 1, 4, or 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sel_start_year</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>First year the fleet's time-varying selectivity deviations are estimated and penalized (NA -&gt; earliest year of data across fleets sharing the Selectivity_index, bounded below by styr).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bin_first_selected</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Age/length bin at which selectivity becomes non-zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sel_shape_sd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Shape/smoothness selectivity penalty expressed as a standard deviation (an intuitive alternative to Sel_curve_pen1); weight = 1/(2*sd^2). NonParametric (2/9) and LogisticPM (11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sel_curvature_sd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2nd-difference curvature selectivity penalty expressed as a standard deviation (Sel_curve_pen2); NonParametric-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sel_devmag_sd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Deviation-magnitude selectivity penalty expressed as a standard deviation (Sel_curve_pen3). NonParametric (2/9) and LogisticPM (11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sel_shape_dir</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Direction of the (directional-mode) NonParametric shape penalty when Sel_shape_sd is used: "Decreasing" (default) or "Increasing".</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sel_pen_first_bin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>First bin (age or length) for the non-parametric shape penalty (NA -&gt; Bin_first_selected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sel_pen_last_bin</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Last (left) bin of the shape-penalty pairs (NA -&gt; nbins-2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sel_shape_mode</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Shape-penalty mode: "Directional" (default) or "Smooth" (two-sided d^2, RTMB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sel_avgsel_pen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Weight on the AMAK avgsel base-level penalty (type 9); 0 = off (default), 10 matches AMAK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sel_cap_bin</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NonParametricRPM bin cap (NA -&gt; no cap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sel_norm_bin</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Age/length bin at which selectivity = 1. _x000D_
 If NA, it will not normalize selectivity. _x000D_
@@ -934,35 +1138,35 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Sel_norm_bin2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Age_max_selected` and `Age_max_selected_upper`</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sel_norm_bin_upper</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Upper age/length bin for selectivity normalization (default = NA). If NA, does not use the age range, If not NA, uses mean selectivity between `Sel_norm_bin` and `Sel_norm_bin_upper`</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Comp_loglike</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Comp_distribution</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 -1 = AFSC multinomial_x000D_
@@ -971,36 +1175,36 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Comp_weights</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Composition weights for composition likelihood. _x000D_
 After running model, these will update to McAllister &amp; Ianelli 1997 weights using the harmonic mean.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CAAL_loglike</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CAAL_distribution</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Composition data distribution:_x000D_
 0 = full multinomial_x000D_
@@ -1008,161 +1212,161 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>CAAL_weights</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Composition weights for CAAL  likelihood.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>weight1_Numbers2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Observation_units</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>1 = catch/index is weight (kg) the observation _x000D_
 2 = catch/index is in numbers</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Weight_index</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Weight index to use for calculation of derived quantities</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Age_transition_index</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) index to used convert age to length</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Q_index</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Catchability_index</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>index to use if catchability coefficients are to be set the same</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Catchability</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>0 = fixed at "Q_sd_prior" _x000D_
 1 = Estimate as free parameter; _x000D_
 2 = Estimate as free parameter with normal prior of N(Q_prior, Q_sd_prior)_x000D_
 3 = Estimate analytically following Ludwig and Walters 1994_x000D_
 4 = Estimate power equation (NOT YET IMPLEMENTED)_x000D_
-5 = Linear equation log(q_y) = q_mu + beta * index_y)_x000D_
-6 = AR1 random deviates fit to environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+5 = Linear equation log(q_y) = q_mu + beta * index_y). Indices are comma seperated and specified by Time_varying_q_x000D_
+6 = AR1 random deviates fit to environmental index (sensu Rogers et al 2024; 10.1093/icesjms/fsae005). Index is specified by Time_varying_q</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Q_prior</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Catchability_init</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Starting value or fixed value for catchability</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Q_sd_prior</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Catchability_prior_sd</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Standard deviation for q prior</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Time_varying_q</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>0 = no_x000D_
 1 = penalized deviate or random effect _x000D_
@@ -1173,35 +1377,35 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Time_varying_q_sd_prior</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Time_varying_q_sd</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>starting or fixed sd to use for the random walk of time varying q if set to 1</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Estimate_index_sd</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from index_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1209,35 +1413,35 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Index_sd_prior</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Index_sd</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>Starting value to be used if "Estimate_index_sd" = 1</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Estimate_catch_sd</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>0 = use input "Log_sd" from catch_data_x000D_
 1 = estimate as free parameter_x000D_
@@ -1245,186 +1449,220 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Catch_sd_prior</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Catch_sd</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>Starting value to be used if Estimate_catch_sd = 1</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>fleet_control</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>proj_F_prop</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Index_distribution</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Survey/index biomass observation likelihood family. 0 or "Lognormal" (default) = independent lognormal; "MVN"/"MVNORM" use a multivariate normal with a user-supplied covariance in index_cov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Observation month for the fleet (0 = not specified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fleet_control</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Proj_F_proportion</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>The proportion of future fishing mortality assigned to this fleet</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>index_data</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Survey index or fishery indices in weight (kg) or numbers.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>catch_data</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Total catch in weight (kg) or numbers data</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Total catch in weight (mt) or numbers data</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>comp_data</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Survey/fishery age or length composition data. Note if sex is 3, put female composition data then male composition data (similar to SS).</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>caal_data</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Survey/fishery CAAL data. Note if sex is 3, put female CAAL data then male CAAL data (similar to SS).</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>emp_sel</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Empirical/fixed selectivity for surveys and fisheries (leave empty if not used)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>age_trans_matrix</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Age transition matrix (e.g. growth trajectory) used to convert age to length for length comp data. _x000D_
 Can have multiple matrices for a species specified by Age_transition_index.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>age_error</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Aging error matrices. Can have only one per species.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Time-invariant or -varying empirical weight-at-age for calculation of derived quantities (SSB, Consumption/Ration, Suitability, Total Catch, Survey Biomass, etc). _x000D_
 Can have multiple weight-at-age data-sets for each species.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>maturity</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Maturity-at-age for each species</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>sex_ratio</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Percent female at age for each species</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>M1_base</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Residual natural mortality for each species</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>bioenergetics_control</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Ceq</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Integer: switch for which bioenergetics equation to use for each species for ft to scale max consumtion: _x000D_
 1 = Exponential (Stewart et al 1983)_x000D_
@@ -1434,231 +1672,265 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Cindex</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Pvalue</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>fday</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Numeric: number of foraging days per year for each species</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Qc</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Tco</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Tcm</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Tcl</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>CK1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>bioenergetics_control</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>CK4</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>env_data</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>ration_data</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
-        </is>
-      </c>
-    </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cindex</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Integer: which environmental index in env_data to use to drive bioenergetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pvalue</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Numeric: this scales the maximum consumption used for ration for each species; Pvalue is in Cmax*fT*Pvalue*Pyrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>fday</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Numeric: number of foraging days per year for each species</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Intercept of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Slope of allometric mass function for calculating maximum consumption: CA * Weight ^ CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Qc</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tco</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tcm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tcl</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CK1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CK4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Parameter for temperature scaling function of maximum consumption specified by Ceq</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Diet_distribution</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Diet composition likelihood distribution per predator species (0 = multinomial).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>bioenergetics_control</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Diet_comp_weights</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Diet composition weight (multinomial multiplier) per predator species.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>env_data</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Environmental indices such as bottom temperature data to incorporate into ration equation specificed by Ceq and Cindex. Also used to drive catchability if Estimate_q = 5 or 6. Will use the mean for missing years. Temperature should be in celcius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ration_data</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Annual relative foraging rate by age. Multiplied by pvalue and fday to scale maximum consumption to the number of days in a year that foraging occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>diet_data</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Stomach proportion by weight for each predator, prey, predator age, prey age combination. Multiple diet-data formats can be included:_x000D_
 _x000D_
 1) If Pred_age &gt;= 0 and Prey_age &gt;= 0, data is assumed to be  diet proportion of prey-at-age/sex in predator-at-age/sex. _x000D_
 2) If Pred_age &gt;= 0 and Prey_age &lt; 0, data is assumed to be mean diet proportion of prey-spp in predator-at-age/sex (sum across prey ages and sexes)_x000D_
 3) If Pred_age &lt; 0 and Prey_age &lt; 0, data is assumed to be  mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take mean across predator ages/sexes)_x000D_
-4) If Pred_age &lt; -500 and Prey_age &lt; 0, data is assumed to be weighted mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take weighted mean across predator ages/sexes). Weights are estimated predators-at-age._x000D_
+4) If Pred_age &lt; -500 and Prey_age &lt; 0, data is assumed to be weighted mean diet proportion of prey-spp in predator-spp (sum across prey ages/sexes and take weighted mean across predator ages/sexes). Weights are estimated predators-at-age. _x000D_
 _x000D_
 If "Year = 0", the the diet will be assumed to be the average between "suit_styr" and "suit_endyr". _x000D_
 _x000D_
@@ -1666,51 +1938,36 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>0 = combined_x000D_
-1 = use female only _x000D_
-2 = use male only_x000D_
-3 = joint female and male</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>NOTE: Most objects are ordered by species code if not specified</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>NOTE: Lengths are index 1 through nlenths</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>NOTE: Columns for ages are index by 1 trhough nages, but are place holders.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>NOTE: For catch, index, and comp data, if "Year" is negative, it will predict for that year, but not include the data in the likelihood.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>NOTE: For emp_sel, weight, and ration_data, if "Year" == 0, those data will be used for all years</t>
         </is>
@@ -2007,25 +2264,25 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>0.0003</v>
+        <v>0.0003000300030003</v>
       </c>
       <c r="G4">
-        <v>0.1435</v>
+        <v>0.1435143514351435</v>
       </c>
       <c r="H4">
-        <v>0.6321</v>
+        <v>0.6321632163216322</v>
       </c>
       <c r="I4">
-        <v>0.1893</v>
+        <v>0.1893189318931893</v>
       </c>
       <c r="J4">
-        <v>0.0333</v>
+        <v>0.03330333033303331</v>
       </c>
       <c r="K4">
-        <v>0.0013</v>
+        <v>0.0013001300130013</v>
       </c>
       <c r="L4">
-        <v>0.0001</v>
+        <v>0.0001000100010001</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2065,25 +2322,25 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.0007</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="H5">
         <v>0.1306</v>
       </c>
       <c r="I5">
-        <v>0.5199</v>
+        <v>0.5199000000000001</v>
       </c>
       <c r="J5">
         <v>0.303</v>
       </c>
       <c r="K5">
-        <v>0.0396</v>
+        <v>0.03960000000000001</v>
       </c>
       <c r="L5">
-        <v>0.0057</v>
+        <v>0.005700000000000001</v>
       </c>
       <c r="M5">
-        <v>0.0005</v>
+        <v>0.0005000000000000001</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2123,34 +2380,34 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.0135</v>
+        <v>0.0134986501349865</v>
       </c>
       <c r="I6">
-        <v>0.2425</v>
+        <v>0.2424757524247575</v>
       </c>
       <c r="J6">
-        <v>0.3999</v>
+        <v>0.3998600139986001</v>
       </c>
       <c r="K6">
-        <v>0.2304</v>
+        <v>0.2303769623037696</v>
       </c>
       <c r="L6">
-        <v>0.0883</v>
+        <v>0.08829117088291172</v>
       </c>
       <c r="M6">
-        <v>0.0212</v>
+        <v>0.0211978802119788</v>
       </c>
       <c r="N6">
-        <v>0.0032</v>
+        <v>0.0031996800319968</v>
       </c>
       <c r="O6">
-        <v>0.0007</v>
+        <v>0.0006999300069993001</v>
       </c>
       <c r="P6">
-        <v>0.0003</v>
+        <v>0.0002999700029997</v>
       </c>
       <c r="Q6">
-        <v>0.0001</v>
+        <v>9.999000099990002E-05</v>
       </c>
     </row>
     <row r="7">
@@ -2233,34 +2490,34 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.0005999999999999999</v>
+        <v>0.0006000600060006001</v>
       </c>
       <c r="I8">
-        <v>0.0195</v>
+        <v>0.0195019501950195</v>
       </c>
       <c r="J8">
-        <v>0.0699</v>
+        <v>0.06990699069906992</v>
       </c>
       <c r="K8">
-        <v>0.1734</v>
+        <v>0.1734173417341734</v>
       </c>
       <c r="L8">
-        <v>0.2077</v>
+        <v>0.2077207720772077</v>
       </c>
       <c r="M8">
-        <v>0.189</v>
+        <v>0.1890189018901891</v>
       </c>
       <c r="N8">
-        <v>0.1308</v>
+        <v>0.1308130813081308</v>
       </c>
       <c r="O8">
-        <v>0.08790000000000001</v>
+        <v>0.08790879087908793</v>
       </c>
       <c r="P8">
-        <v>0.0688</v>
+        <v>0.06880688068806881</v>
       </c>
       <c r="Q8">
-        <v>0.0523</v>
+        <v>0.05230523052305231</v>
       </c>
     </row>
     <row r="9">
@@ -2288,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0.0002</v>
+        <v>0.0002000000000000001</v>
       </c>
       <c r="I9">
-        <v>0.0077</v>
+        <v>0.007700000000000002</v>
       </c>
       <c r="J9">
         <v>0.0321</v>
@@ -2401,31 +2658,31 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.0012</v>
+        <v>0.0011998800119988</v>
       </c>
       <c r="J11">
-        <v>0.0075</v>
+        <v>0.007499250074992502</v>
       </c>
       <c r="K11">
-        <v>0.0423</v>
+        <v>0.04229577042295771</v>
       </c>
       <c r="L11">
-        <v>0.0871</v>
+        <v>0.08709129087091293</v>
       </c>
       <c r="M11">
-        <v>0.1413</v>
+        <v>0.1412858714128588</v>
       </c>
       <c r="N11">
-        <v>0.1805</v>
+        <v>0.1804819518048195</v>
       </c>
       <c r="O11">
-        <v>0.1861</v>
+        <v>0.186081391860814</v>
       </c>
       <c r="P11">
-        <v>0.1816</v>
+        <v>0.1815818418158185</v>
       </c>
       <c r="Q11">
-        <v>0.1725</v>
+        <v>0.1724827517248275</v>
       </c>
     </row>
     <row r="12">
@@ -2447,22 +2704,22 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.321</v>
+        <v>0.3213213213213214</v>
       </c>
       <c r="G12">
-        <v>0.337</v>
+        <v>0.3373373373373373</v>
       </c>
       <c r="H12">
-        <v>0.241</v>
+        <v>0.2412412412412412</v>
       </c>
       <c r="I12">
-        <v>0.08500000000000001</v>
+        <v>0.0850850850850851</v>
       </c>
       <c r="J12">
-        <v>0.014</v>
+        <v>0.01401401401401401</v>
       </c>
       <c r="K12">
-        <v>0.001</v>
+        <v>0.001001001001001001</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2544,34 +2801,34 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.002</v>
+        <v>0.002002002002002002</v>
       </c>
       <c r="H13">
-        <v>0.011</v>
+        <v>0.01101101101101101</v>
       </c>
       <c r="I13">
-        <v>0.048</v>
+        <v>0.04804804804804804</v>
       </c>
       <c r="J13">
-        <v>0.135</v>
+        <v>0.1351351351351351</v>
       </c>
       <c r="K13">
-        <v>0.24</v>
+        <v>0.2402402402402402</v>
       </c>
       <c r="L13">
-        <v>0.267</v>
+        <v>0.2672672672672672</v>
       </c>
       <c r="M13">
-        <v>0.187</v>
+        <v>0.1871871871871872</v>
       </c>
       <c r="N13">
-        <v>0.082</v>
+        <v>0.08208208208208208</v>
       </c>
       <c r="O13">
-        <v>0.023</v>
+        <v>0.02302302302302302</v>
       </c>
       <c r="P13">
-        <v>0.004</v>
+        <v>0.004004004004004004</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2750,34 +3007,34 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.001</v>
+        <v>0.001001001001001001</v>
       </c>
       <c r="N15">
-        <v>0.006</v>
+        <v>0.006006006006006006</v>
       </c>
       <c r="O15">
-        <v>0.02</v>
+        <v>0.02002002002002002</v>
       </c>
       <c r="P15">
-        <v>0.053</v>
+        <v>0.05305305305305305</v>
       </c>
       <c r="Q15">
-        <v>0.109</v>
+        <v>0.1091091091091091</v>
       </c>
       <c r="R15">
-        <v>0.308</v>
+        <v>0.3083083083083083</v>
       </c>
       <c r="S15">
-        <v>0.31</v>
+        <v>0.3103103103103103</v>
       </c>
       <c r="T15">
-        <v>0.152</v>
+        <v>0.1521521521521521</v>
       </c>
       <c r="U15">
-        <v>0.036</v>
+        <v>0.03603603603603604</v>
       </c>
       <c r="V15">
-        <v>0.004</v>
+        <v>0.004004004004004004</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -2850,34 +3107,34 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0.001</v>
+        <v>0.000999000999000999</v>
       </c>
       <c r="P16">
-        <v>0.003</v>
+        <v>0.002997002997002997</v>
       </c>
       <c r="Q16">
-        <v>0.01</v>
+        <v>0.009990009990009988</v>
       </c>
       <c r="R16">
-        <v>0.065</v>
+        <v>0.06493506493506493</v>
       </c>
       <c r="S16">
-        <v>0.191</v>
+        <v>0.1908091908091908</v>
       </c>
       <c r="T16">
-        <v>0.304</v>
+        <v>0.3036963036963037</v>
       </c>
       <c r="U16">
-        <v>0.264</v>
+        <v>0.2637362637362637</v>
       </c>
       <c r="V16">
-        <v>0.125</v>
+        <v>0.1248751248751249</v>
       </c>
       <c r="W16">
-        <v>0.033</v>
+        <v>0.03296703296703297</v>
       </c>
       <c r="X16">
-        <v>0.005</v>
+        <v>0.004995004995004994</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -2950,34 +3207,34 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0.001</v>
+        <v>0.0009990009990009992</v>
       </c>
       <c r="R17">
-        <v>0.007</v>
+        <v>0.006993006993006994</v>
       </c>
       <c r="S17">
-        <v>0.038</v>
+        <v>0.03796203796203797</v>
       </c>
       <c r="T17">
-        <v>0.126</v>
+        <v>0.1258741258741259</v>
       </c>
       <c r="U17">
-        <v>0.247</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="V17">
-        <v>0.286</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W17">
-        <v>0.195</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="X17">
-        <v>0.079</v>
+        <v>0.07892107892107893</v>
       </c>
       <c r="Y17">
-        <v>0.019</v>
+        <v>0.01898101898101898</v>
       </c>
       <c r="Z17">
-        <v>0.003</v>
+        <v>0.002997002997002997</v>
       </c>
       <c r="AA17">
         <v>0</v>
@@ -3047,37 +3304,37 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>0.001</v>
+        <v>0.0009990009990009992</v>
       </c>
       <c r="S18">
-        <v>0.006</v>
+        <v>0.005994005994005995</v>
       </c>
       <c r="T18">
-        <v>0.03</v>
+        <v>0.02997002997002997</v>
       </c>
       <c r="U18">
-        <v>0.101</v>
+        <v>0.1008991008991009</v>
       </c>
       <c r="V18">
-        <v>0.21</v>
+        <v>0.2097902097902098</v>
       </c>
       <c r="W18">
-        <v>0.274</v>
+        <v>0.2737262737262738</v>
       </c>
       <c r="X18">
-        <v>0.222</v>
+        <v>0.2217782217782218</v>
       </c>
       <c r="Y18">
-        <v>0.113</v>
+        <v>0.1128871128871129</v>
       </c>
       <c r="Z18">
-        <v>0.036</v>
+        <v>0.03596403596403597</v>
       </c>
       <c r="AA18">
-        <v>0.007</v>
+        <v>0.006993006993006994</v>
       </c>
       <c r="AB18">
-        <v>0.001</v>
+        <v>0.0009990009990009992</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3338,34 +3595,34 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.003</v>
+        <v>0.002997002997002997</v>
       </c>
       <c r="V21">
-        <v>0.014</v>
+        <v>0.01398601398601399</v>
       </c>
       <c r="W21">
-        <v>0.05</v>
+        <v>0.04995004995004996</v>
       </c>
       <c r="X21">
-        <v>0.124</v>
+        <v>0.1238761238761239</v>
       </c>
       <c r="Y21">
-        <v>0.21</v>
+        <v>0.2097902097902098</v>
       </c>
       <c r="Z21">
-        <v>0.245</v>
+        <v>0.2447552447552448</v>
       </c>
       <c r="AA21">
-        <v>0.195</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="AB21">
-        <v>0.107</v>
+        <v>0.1068931068931069</v>
       </c>
       <c r="AC21">
-        <v>0.04</v>
+        <v>0.03996003996003997</v>
       </c>
       <c r="AD21">
-        <v>0.013</v>
+        <v>0.01298701298701299</v>
       </c>
     </row>
     <row r="22">
@@ -3432,34 +3689,34 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0.001</v>
+        <v>0.000998003992015968</v>
       </c>
       <c r="V22">
-        <v>0.006</v>
+        <v>0.005988023952095809</v>
       </c>
       <c r="W22">
-        <v>0.024</v>
+        <v>0.02395209580838323</v>
       </c>
       <c r="X22">
-        <v>0.07199999999999999</v>
+        <v>0.0718562874251497</v>
       </c>
       <c r="Y22">
-        <v>0.152</v>
+        <v>0.1516966067864271</v>
       </c>
       <c r="Z22">
-        <v>0.224</v>
+        <v>0.2235528942115768</v>
       </c>
       <c r="AA22">
-        <v>0.232</v>
+        <v>0.2315369261477046</v>
       </c>
       <c r="AB22">
-        <v>0.167</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AC22">
-        <v>0.08500000000000001</v>
+        <v>0.08483033932135729</v>
       </c>
       <c r="AD22">
-        <v>0.039</v>
+        <v>0.03892215568862276</v>
       </c>
     </row>
     <row r="23">
@@ -3669,28 +3926,28 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>0.002505225</v>
+        <v>0.002505225010245877</v>
       </c>
       <c r="G25">
-        <v>0.534287239</v>
+        <v>0.5342872411851296</v>
       </c>
       <c r="H25">
-        <v>0.399923215</v>
+        <v>0.3999232166356072</v>
       </c>
       <c r="I25">
-        <v>0.061739832</v>
+        <v>0.06173983225250376</v>
       </c>
       <c r="J25">
-        <v>0.001538802</v>
+        <v>0.001538802006293397</v>
       </c>
       <c r="K25">
-        <v>5.68E-06</v>
+        <v>5.680000023230081E-06</v>
       </c>
       <c r="L25">
-        <v>2.91E-09</v>
+        <v>2.910000011901327E-09</v>
       </c>
       <c r="M25">
-        <v>1.97E-13</v>
+        <v>1.970000008056912E-13</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -3763,43 +4020,43 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>7.36E-08</v>
+        <v>7.360000055362685E-08</v>
       </c>
       <c r="G26">
-        <v>0.000825826</v>
+        <v>0.000825826006211949</v>
       </c>
       <c r="H26">
-        <v>0.016545727</v>
+        <v>0.01654572712445868</v>
       </c>
       <c r="I26">
-        <v>0.120766263</v>
+        <v>0.1207662639084164</v>
       </c>
       <c r="J26">
-        <v>0.331134894</v>
+        <v>0.3311348964908311</v>
       </c>
       <c r="K26">
-        <v>0.354220093</v>
+        <v>0.3542200956644804</v>
       </c>
       <c r="L26">
-        <v>0.150041877</v>
+        <v>0.1500418781286306</v>
       </c>
       <c r="M26">
-        <v>0.024863824</v>
+        <v>0.02486382418702827</v>
       </c>
       <c r="N26">
-        <v>0.001564913</v>
+        <v>0.001564913011771438</v>
       </c>
       <c r="O26">
-        <v>3.62E-05</v>
+        <v>3.620000027230017E-05</v>
       </c>
       <c r="P26">
-        <v>3.01E-07</v>
+        <v>3.010000022641533E-07</v>
       </c>
       <c r="Q26">
-        <v>8.77E-10</v>
+        <v>8.770000065968852E-10</v>
       </c>
       <c r="R26">
-        <v>8.96E-13</v>
+        <v>8.960000067398052E-13</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3857,55 +4114,55 @@
         <v>4</v>
       </c>
       <c r="F27">
-        <v>4.36E-11</v>
+        <v>4.359999933406914E-11</v>
       </c>
       <c r="G27">
-        <v>8.27E-07</v>
+        <v>8.269999873686969E-07</v>
       </c>
       <c r="H27">
-        <v>3.67E-05</v>
+        <v>3.669999943945728E-05</v>
       </c>
       <c r="I27">
-        <v>0.000812507</v>
+        <v>0.0008125069875900578</v>
       </c>
       <c r="J27">
-        <v>0.009056417000000001</v>
+        <v>0.009056416861675517</v>
       </c>
       <c r="K27">
-        <v>0.052400189</v>
+        <v>0.05240018819965819</v>
       </c>
       <c r="L27">
-        <v>0.163307487</v>
+        <v>0.1633074845056997</v>
       </c>
       <c r="M27">
-        <v>0.283683539</v>
+        <v>0.2836835346671188</v>
       </c>
       <c r="N27">
-        <v>0.279435081</v>
+        <v>0.2794350767320082</v>
       </c>
       <c r="O27">
-        <v>0.155133163</v>
+        <v>0.1551331606305514</v>
       </c>
       <c r="P27">
-        <v>0.047544266</v>
+        <v>0.04754426527382583</v>
       </c>
       <c r="Q27">
-        <v>0.007866402999999999</v>
+        <v>0.007866402879851365</v>
       </c>
       <c r="R27">
-        <v>0.000690862</v>
+        <v>0.0006908619894480201</v>
       </c>
       <c r="S27">
-        <v>3.23E-05</v>
+        <v>3.229999950666132E-05</v>
       </c>
       <c r="T27">
-        <v>2.74E-07</v>
+        <v>2.739999958150217E-07</v>
       </c>
       <c r="U27">
-        <v>2.3E-10</v>
+        <v>2.29999996487062E-10</v>
       </c>
       <c r="V27">
-        <v>4.39E-14</v>
+        <v>4.389999932948705E-14</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -3951,64 +4208,64 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>3.07E-13</v>
+        <v>3.070000007921986E-13</v>
       </c>
       <c r="G28">
-        <v>4.26E-09</v>
+        <v>4.260000010992723E-09</v>
       </c>
       <c r="H28">
-        <v>2.16E-07</v>
+        <v>2.160000005573775E-07</v>
       </c>
       <c r="I28">
-        <v>6.55E-06</v>
+        <v>6.550000016901957E-06</v>
       </c>
       <c r="J28">
-        <v>0.000118811</v>
+        <v>0.000118811000306586</v>
       </c>
       <c r="K28">
-        <v>0.001296239</v>
+        <v>0.001296239003344882</v>
       </c>
       <c r="L28">
-        <v>0.008695438</v>
+        <v>0.008695438022438155</v>
       </c>
       <c r="M28">
-        <v>0.036896697</v>
+        <v>0.03689669709521014</v>
       </c>
       <c r="N28">
-        <v>0.102568596</v>
+        <v>0.1025685962646733</v>
       </c>
       <c r="O28">
-        <v>0.192886707</v>
+        <v>0.1928867074977348</v>
       </c>
       <c r="P28">
-        <v>0.248909902</v>
+        <v>0.2489099026422999</v>
       </c>
       <c r="Q28">
-        <v>0.218476057</v>
+        <v>0.2184760575637669</v>
       </c>
       <c r="R28">
-        <v>0.127656989</v>
+        <v>0.1276569893294127</v>
       </c>
       <c r="S28">
-        <v>0.053535571</v>
+        <v>0.05353557113814594</v>
       </c>
       <c r="T28">
-        <v>0.00858831</v>
+        <v>0.008588310022161717</v>
       </c>
       <c r="U28">
-        <v>0.00035841</v>
+        <v>0.0003584100009248596</v>
       </c>
       <c r="V28">
-        <v>5.47E-06</v>
+        <v>5.47000001411507E-06</v>
       </c>
       <c r="W28">
-        <v>3.01E-08</v>
+        <v>3.010000007767159E-08</v>
       </c>
       <c r="X28">
-        <v>5.92E-11</v>
+        <v>5.920000015276273E-11</v>
       </c>
       <c r="Y28">
-        <v>4.14E-14</v>
+        <v>4.140000010683069E-14</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4045,67 +4302,67 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>1.12E-14</v>
+        <v>1.119999992816084E-14</v>
       </c>
       <c r="G29">
-        <v>9.42E-11</v>
+        <v>9.41999993957813E-11</v>
       </c>
       <c r="H29">
-        <v>4.42E-09</v>
+        <v>4.419999971649187E-09</v>
       </c>
       <c r="I29">
-        <v>1.4E-07</v>
+        <v>1.399999991020105E-07</v>
       </c>
       <c r="J29">
-        <v>2.91E-06</v>
+        <v>2.909999981334646E-06</v>
       </c>
       <c r="K29">
-        <v>4.07E-05</v>
+        <v>4.069999973894161E-05</v>
       </c>
       <c r="L29">
-        <v>0.000381616</v>
+        <v>0.0003816159975522344</v>
       </c>
       <c r="M29">
-        <v>0.002440409</v>
+        <v>0.002440408984346702</v>
       </c>
       <c r="N29">
-        <v>0.010850744</v>
+        <v>0.01085074393040104</v>
       </c>
       <c r="O29">
-        <v>0.03454733</v>
+        <v>0.03454732977840613</v>
       </c>
       <c r="P29">
-        <v>0.081562906</v>
+        <v>0.08156290547683831</v>
       </c>
       <c r="Q29">
-        <v>0.146875019</v>
+        <v>0.1468750180579126</v>
       </c>
       <c r="R29">
-        <v>0.20323132</v>
+        <v>0.2032313186964314</v>
       </c>
       <c r="S29">
-        <v>0.260234558</v>
+        <v>0.2602345563308006</v>
       </c>
       <c r="T29">
-        <v>0.192724341</v>
+        <v>0.1927243397638254</v>
       </c>
       <c r="U29">
-        <v>0.058124311</v>
+        <v>0.0581243106271784</v>
       </c>
       <c r="V29">
-        <v>0.008393196</v>
+        <v>0.008393195946164269</v>
       </c>
       <c r="W29">
-        <v>0.00057203</v>
+        <v>0.0005720299963308787</v>
       </c>
       <c r="X29">
-        <v>1.82E-05</v>
+        <v>1.819999988326136E-05</v>
       </c>
       <c r="Y29">
-        <v>2.7E-07</v>
+        <v>2.69999998268163E-07</v>
       </c>
       <c r="Z29">
-        <v>1.9E-09</v>
+        <v>1.899999987812999E-09</v>
       </c>
       <c r="AA29">
         <v>0</v>
@@ -4139,73 +4396,73 @@
         <v>7</v>
       </c>
       <c r="F30">
-        <v>1.19E-15</v>
+        <v>1.190000009991399E-15</v>
       </c>
       <c r="G30">
-        <v>6.13E-12</v>
+        <v>6.130000051468299E-12</v>
       </c>
       <c r="H30">
-        <v>2.49E-10</v>
+        <v>2.490000020906373E-10</v>
       </c>
       <c r="I30">
-        <v>7.33E-09</v>
+        <v>7.33000006154366E-09</v>
       </c>
       <c r="J30">
-        <v>1.54E-07</v>
+        <v>1.540000012930046E-07</v>
       </c>
       <c r="K30">
-        <v>2.31E-06</v>
+        <v>2.310000019395069E-06</v>
       </c>
       <c r="L30">
-        <v>2.49E-05</v>
+        <v>2.490000020906373E-05</v>
       </c>
       <c r="M30">
-        <v>0.000194666</v>
+        <v>0.0001946660016344417</v>
       </c>
       <c r="N30">
-        <v>0.001107713</v>
+        <v>0.001107713009300506</v>
       </c>
       <c r="O30">
-        <v>0.004667623</v>
+        <v>0.004667623039189986</v>
       </c>
       <c r="P30">
-        <v>0.014910713</v>
+        <v>0.01491071312519234</v>
       </c>
       <c r="Q30">
-        <v>0.037291511</v>
+        <v>0.03729151131310451</v>
       </c>
       <c r="R30">
-        <v>0.07551313699999999</v>
+        <v>0.07551313763401839</v>
       </c>
       <c r="S30">
-        <v>0.166204335</v>
+        <v>0.1662043363954738</v>
       </c>
       <c r="T30">
-        <v>0.279279279</v>
+        <v>0.2792792813448661</v>
       </c>
       <c r="U30">
-        <v>0.249389041</v>
+        <v>0.2493890430939037</v>
       </c>
       <c r="V30">
-        <v>0.128161274</v>
+        <v>0.1281612750760592</v>
       </c>
       <c r="W30">
-        <v>0.03685801</v>
+        <v>0.03685801030946478</v>
       </c>
       <c r="X30">
-        <v>0.005858588</v>
+        <v>0.005858588049189487</v>
       </c>
       <c r="Y30">
-        <v>0.00051173</v>
+        <v>0.0005117300042965534</v>
       </c>
       <c r="Z30">
-        <v>2.5E-05</v>
+        <v>2.500000020990334E-05</v>
       </c>
       <c r="AA30">
-        <v>1.87E-11</v>
+        <v>1.87000001570077E-11</v>
       </c>
       <c r="AB30">
-        <v>3.5E-14</v>
+        <v>3.500000029386468E-14</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -4233,76 +4490,76 @@
         <v>8</v>
       </c>
       <c r="F31">
-        <v>2.71E-16</v>
+        <v>2.710000115044643E-16</v>
       </c>
       <c r="G31">
-        <v>8.74E-13</v>
+        <v>8.740000371029585E-13</v>
       </c>
       <c r="H31">
-        <v>3E-11</v>
+        <v>3.000000127355693E-11</v>
       </c>
       <c r="I31">
-        <v>7.92E-10</v>
+        <v>7.920000336219028E-10</v>
       </c>
       <c r="J31">
-        <v>1.57E-08</v>
+        <v>1.570000066649479E-08</v>
       </c>
       <c r="K31">
-        <v>2.35E-07</v>
+        <v>2.350000099761959E-07</v>
       </c>
       <c r="L31">
-        <v>2.64E-06</v>
+        <v>2.64000011207301E-06</v>
       </c>
       <c r="M31">
-        <v>2.25E-05</v>
+        <v>2.25000009551677E-05</v>
       </c>
       <c r="N31">
-        <v>0.00014589</v>
+        <v>0.0001458900061933073</v>
       </c>
       <c r="O31">
-        <v>0.000722513</v>
+        <v>0.0007225130306720479</v>
       </c>
       <c r="P31">
-        <v>0.002770738</v>
+        <v>0.002770738117623086</v>
       </c>
       <c r="Q31">
-        <v>0.008390322</v>
+        <v>0.008390322356185091</v>
       </c>
       <c r="R31">
-        <v>0.020644402</v>
+        <v>0.02064440287639404</v>
       </c>
       <c r="S31">
-        <v>0.058544251</v>
+        <v>0.05854425348531454</v>
       </c>
       <c r="T31">
-        <v>0.146928956</v>
+        <v>0.146928962237413</v>
       </c>
       <c r="U31">
-        <v>0.23516876</v>
+        <v>0.2351687699833601</v>
       </c>
       <c r="V31">
-        <v>0.25362598</v>
+        <v>0.2536259907669041</v>
       </c>
       <c r="W31">
-        <v>0.174960068</v>
+        <v>0.1749600754273869</v>
       </c>
       <c r="X31">
-        <v>0.07504192899999999</v>
+        <v>0.07504193218567227</v>
       </c>
       <c r="Y31">
-        <v>0.019781022</v>
+        <v>0.01978102283974192</v>
       </c>
       <c r="Z31">
-        <v>0.003249649</v>
+        <v>0.003249649137953766</v>
       </c>
       <c r="AA31">
-        <v>8.52E-08</v>
+        <v>8.520000361690167E-08</v>
       </c>
       <c r="AB31">
-        <v>8.21E-10</v>
+        <v>8.210000348530078E-10</v>
       </c>
       <c r="AC31">
-        <v>4.23E-12</v>
+        <v>4.230000179571527E-12</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4327,79 +4584,79 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>1.09E-16</v>
+        <v>1.089999942074241E-16</v>
       </c>
       <c r="G32">
-        <v>2.21E-13</v>
+        <v>2.209999882554195E-13</v>
       </c>
       <c r="H32">
-        <v>6.48E-12</v>
+        <v>6.47999965563402E-12</v>
       </c>
       <c r="I32">
-        <v>1.52E-10</v>
+        <v>1.519999919222795E-10</v>
       </c>
       <c r="J32">
-        <v>2.77E-09</v>
+        <v>2.769999852794172E-09</v>
       </c>
       <c r="K32">
-        <v>3.97E-08</v>
+        <v>3.969999789022694E-08</v>
       </c>
       <c r="L32">
-        <v>4.42E-07</v>
+        <v>4.41999976510839E-07</v>
       </c>
       <c r="M32">
-        <v>3.87E-06</v>
+        <v>3.869999794336985E-06</v>
       </c>
       <c r="N32">
-        <v>2.66E-05</v>
+        <v>2.659999858639891E-05</v>
       </c>
       <c r="O32">
-        <v>0.00014379</v>
+        <v>0.0001437899923585827</v>
       </c>
       <c r="P32">
-        <v>0.000616765</v>
+        <v>0.0006167649672233204</v>
       </c>
       <c r="Q32">
-        <v>0.002119279</v>
+        <v>0.002119278887375372</v>
       </c>
       <c r="R32">
-        <v>0.005932753</v>
+        <v>0.005932752684716312</v>
       </c>
       <c r="S32">
-        <v>0.019500586</v>
+        <v>0.01950058496368234</v>
       </c>
       <c r="T32">
-        <v>0.059394347</v>
+        <v>0.05939434384361227</v>
       </c>
       <c r="U32">
-        <v>0.125971312</v>
+        <v>0.1259713053055194</v>
       </c>
       <c r="V32">
-        <v>0.204754511</v>
+        <v>0.2047545001187519</v>
       </c>
       <c r="W32">
-        <v>0.241186369</v>
+        <v>0.2411863561826574</v>
       </c>
       <c r="X32">
-        <v>0.19543744</v>
+        <v>0.195437429613888</v>
       </c>
       <c r="Y32">
-        <v>0.106051772</v>
+        <v>0.1060517663641015</v>
       </c>
       <c r="Z32">
-        <v>0.038845033</v>
+        <v>0.03884503093566237</v>
       </c>
       <c r="AA32">
-        <v>1.47E-05</v>
+        <v>1.46999992187994E-05</v>
       </c>
       <c r="AB32">
-        <v>4.34E-07</v>
+        <v>4.339999769359822E-07</v>
       </c>
       <c r="AC32">
-        <v>7.499999999999999E-09</v>
+        <v>7.499999601428264E-09</v>
       </c>
       <c r="AD32">
-        <v>1.42E-11</v>
+        <v>1.419999924537085E-11</v>
       </c>
     </row>
     <row r="33">
@@ -4421,79 +4678,79 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>5.82E-17</v>
+        <v>5.820000189100768E-17</v>
       </c>
       <c r="G33">
-        <v>9.02E-14</v>
+        <v>9.020000293073697E-14</v>
       </c>
       <c r="H33">
-        <v>2.27E-12</v>
+        <v>2.270000073755797E-12</v>
       </c>
       <c r="I33">
-        <v>4.71E-11</v>
+        <v>4.710000153035157E-11</v>
       </c>
       <c r="J33">
-        <v>7.89E-10</v>
+        <v>7.890000256358256E-10</v>
       </c>
       <c r="K33">
-        <v>1.06E-08</v>
+        <v>1.060000034441033E-08</v>
       </c>
       <c r="L33">
-        <v>1.14E-07</v>
+        <v>1.140000037040356E-07</v>
       </c>
       <c r="M33">
-        <v>9.86E-07</v>
+        <v>9.86000032036659E-07</v>
       </c>
       <c r="N33">
-        <v>6.91E-06</v>
+        <v>6.910000224516546E-06</v>
       </c>
       <c r="O33">
-        <v>3.9E-05</v>
+        <v>3.900000126717009E-05</v>
       </c>
       <c r="P33">
-        <v>0.000178483</v>
+        <v>0.0001784830057991877</v>
       </c>
       <c r="Q33">
-        <v>0.000665363</v>
+        <v>0.000665363021618669</v>
       </c>
       <c r="R33">
-        <v>0.002040134</v>
+        <v>0.002040134066287097</v>
       </c>
       <c r="S33">
-        <v>0.007471086</v>
+        <v>0.007471086242747095</v>
       </c>
       <c r="T33">
-        <v>0.025668481</v>
+        <v>0.0256684818340085</v>
       </c>
       <c r="U33">
-        <v>0.062054837</v>
+        <v>0.06205483901625727</v>
       </c>
       <c r="V33">
-        <v>0.122843401</v>
+        <v>0.1228434049913714</v>
       </c>
       <c r="W33">
-        <v>0.196508893</v>
+        <v>0.1965088993848767</v>
       </c>
       <c r="X33">
-        <v>0.238902166</v>
+        <v>0.2389021737622995</v>
       </c>
       <c r="Y33">
-        <v>0.210158663</v>
+        <v>0.2101586698283787</v>
       </c>
       <c r="Z33">
-        <v>0.133032704</v>
+        <v>0.1330327083224375</v>
       </c>
       <c r="AA33">
-        <v>0.000401548</v>
+        <v>0.0004015480130469132</v>
       </c>
       <c r="AB33">
-        <v>2.61E-05</v>
+        <v>2.610000084802921E-05</v>
       </c>
       <c r="AC33">
-        <v>1.08E-06</v>
+        <v>1.080000035090864E-06</v>
       </c>
       <c r="AD33">
-        <v>7.07E-09</v>
+        <v>7.070000229715193E-09</v>
       </c>
     </row>
     <row r="34">
@@ -4515,79 +4772,79 @@
         <v>11</v>
       </c>
       <c r="F34">
-        <v>6.86E-17</v>
+        <v>6.860000136590314E-17</v>
       </c>
       <c r="G34">
-        <v>5.58E-14</v>
+        <v>5.580000111104075E-14</v>
       </c>
       <c r="H34">
-        <v>1.22E-12</v>
+        <v>1.220000024291572E-12</v>
       </c>
       <c r="I34">
-        <v>2.26E-11</v>
+        <v>2.260000044999142E-11</v>
       </c>
       <c r="J34">
-        <v>3.45E-10</v>
+        <v>3.45000006869338E-10</v>
       </c>
       <c r="K34">
-        <v>4.32E-09</v>
+        <v>4.320000086016058E-09</v>
       </c>
       <c r="L34">
-        <v>4.44E-08</v>
+        <v>4.440000088405393E-08</v>
       </c>
       <c r="M34">
-        <v>3.73E-07</v>
+        <v>3.730000074268495E-07</v>
       </c>
       <c r="N34">
-        <v>2.6E-06</v>
+        <v>2.600000051768924E-06</v>
       </c>
       <c r="O34">
-        <v>1.49E-05</v>
+        <v>1.490000029667576E-05</v>
       </c>
       <c r="P34">
-        <v>7.02E-05</v>
+        <v>7.020000139776095E-05</v>
       </c>
       <c r="Q34">
-        <v>0.000274962</v>
+        <v>0.0002749620054748026</v>
       </c>
       <c r="R34">
-        <v>0.000896336</v>
+        <v>0.0008963360178470578</v>
       </c>
       <c r="S34">
-        <v>0.003558746</v>
+        <v>0.003558746070858635</v>
       </c>
       <c r="T34">
-        <v>0.013436721</v>
+        <v>0.01343672126754023</v>
       </c>
       <c r="U34">
-        <v>0.035171443</v>
+        <v>0.03517144370030298</v>
       </c>
       <c r="V34">
-        <v>0.07568430199999999</v>
+        <v>0.07568430350695957</v>
       </c>
       <c r="W34">
-        <v>0.140531213</v>
+        <v>0.1405312157981345</v>
       </c>
       <c r="X34">
-        <v>0.217737939</v>
+        <v>0.2177379433354072</v>
       </c>
       <c r="Y34">
-        <v>0.264062263</v>
+        <v>0.2640622682577766</v>
       </c>
       <c r="Z34">
-        <v>0.24422033</v>
+        <v>0.2442203348627014</v>
       </c>
       <c r="AA34">
-        <v>0.003853704</v>
+        <v>0.00385370407673158</v>
       </c>
       <c r="AB34">
-        <v>0.000448222</v>
+        <v>0.0004482220089246041</v>
       </c>
       <c r="AC34">
-        <v>3.51E-05</v>
+        <v>3.510000069888047E-05</v>
       </c>
       <c r="AD34">
-        <v>5.77E-07</v>
+        <v>5.770000114887189E-07</v>
       </c>
     </row>
     <row r="35">
@@ -4609,79 +4866,79 @@
         <v>12</v>
       </c>
       <c r="F35">
-        <v>8.84E-17</v>
+        <v>8.839999514503961E-17</v>
       </c>
       <c r="G35">
-        <v>4.8E-14</v>
+        <v>4.799999736382241E-14</v>
       </c>
       <c r="H35">
-        <v>9.21E-13</v>
+        <v>9.209999494183426E-13</v>
       </c>
       <c r="I35">
-        <v>1.54E-11</v>
+        <v>1.539999915422636E-11</v>
       </c>
       <c r="J35">
-        <v>2.14E-10</v>
+        <v>2.139999882470416E-10</v>
       </c>
       <c r="K35">
-        <v>2.49E-09</v>
+        <v>2.489999863248287E-09</v>
       </c>
       <c r="L35">
-        <v>2.42E-08</v>
+        <v>2.419999867092714E-08</v>
       </c>
       <c r="M35">
-        <v>1.97E-07</v>
+        <v>1.969999891806878E-07</v>
       </c>
       <c r="N35">
-        <v>1.34E-06</v>
+        <v>1.339999926406709E-06</v>
       </c>
       <c r="O35">
-        <v>7.63E-06</v>
+        <v>7.629999580957605E-06</v>
       </c>
       <c r="P35">
-        <v>3.65E-05</v>
+        <v>3.649999799540663E-05</v>
       </c>
       <c r="Q35">
-        <v>0.000146448</v>
+        <v>0.0001464479919570222</v>
       </c>
       <c r="R35">
-        <v>0.000495971</v>
+        <v>0.000495970972761091</v>
       </c>
       <c r="S35">
-        <v>0.002084499</v>
+        <v>0.002084498885518551</v>
       </c>
       <c r="T35">
-        <v>0.008485197999999999</v>
+        <v>0.008485197533989818</v>
       </c>
       <c r="U35">
-        <v>0.023715826</v>
+        <v>0.02371582469751815</v>
       </c>
       <c r="V35">
-        <v>0.053255123</v>
+        <v>0.05325512007520913</v>
       </c>
       <c r="W35">
-        <v>0.104629979</v>
+        <v>0.1046299732536832</v>
       </c>
       <c r="X35">
-        <v>0.183557087</v>
+        <v>0.1835570769189775</v>
       </c>
       <c r="Y35">
-        <v>0.272643004</v>
+        <v>0.2726429890263464</v>
       </c>
       <c r="Z35">
-        <v>0.327222826</v>
+        <v>0.3272228080288025</v>
       </c>
       <c r="AA35">
-        <v>0.019707504</v>
+        <v>0.01970750291765666</v>
       </c>
       <c r="AB35">
-        <v>0.003541419</v>
+        <v>0.003541418805503971</v>
       </c>
       <c r="AC35">
-        <v>0.000454477</v>
+        <v>0.0004544769750399567</v>
       </c>
       <c r="AD35">
-        <v>1.5E-05</v>
+        <v>1.499999917619451E-05</v>
       </c>
     </row>
     <row r="36">
@@ -4703,79 +4960,79 @@
         <v>13</v>
       </c>
       <c r="F36">
-        <v>1.16E-16</v>
+        <v>1.159999988874421E-16</v>
       </c>
       <c r="G36">
-        <v>5.07E-14</v>
+        <v>5.069999951373545E-14</v>
       </c>
       <c r="H36">
-        <v>8.66E-13</v>
+        <v>8.659999916941796E-13</v>
       </c>
       <c r="I36">
-        <v>1.31E-11</v>
+        <v>1.309999987435768E-11</v>
       </c>
       <c r="J36">
-        <v>1.67E-10</v>
+        <v>1.669999983983002E-10</v>
       </c>
       <c r="K36">
-        <v>1.81E-09</v>
+        <v>1.80999998264026E-09</v>
       </c>
       <c r="L36">
-        <v>1.66E-08</v>
+        <v>1.659999984078912E-08</v>
       </c>
       <c r="M36">
-        <v>1.3E-07</v>
+        <v>1.299999987531678E-07</v>
       </c>
       <c r="N36">
-        <v>8.53E-07</v>
+        <v>8.529999918188627E-07</v>
       </c>
       <c r="O36">
-        <v>4.8E-06</v>
+        <v>4.79999995396312E-06</v>
       </c>
       <c r="P36">
-        <v>2.29E-05</v>
+        <v>2.289999978036572E-05</v>
       </c>
       <c r="Q36">
-        <v>9.26E-05</v>
+        <v>9.259999911187185E-05</v>
       </c>
       <c r="R36">
-        <v>0.000320283</v>
+        <v>0.0003202829969281604</v>
       </c>
       <c r="S36">
-        <v>0.001397353</v>
+        <v>0.001397352986597964</v>
       </c>
       <c r="T36">
-        <v>0.006018542</v>
+        <v>0.006018541942276062</v>
       </c>
       <c r="U36">
-        <v>0.017806674</v>
+        <v>0.01780667382921589</v>
       </c>
       <c r="V36">
-        <v>0.041414035</v>
+        <v>0.0414140346027973</v>
       </c>
       <c r="W36">
-        <v>0.08279093899999999</v>
+        <v>0.08279093820595071</v>
       </c>
       <c r="X36">
-        <v>0.152128196</v>
+        <v>0.1521281945409359</v>
       </c>
       <c r="Y36">
-        <v>0.253080221</v>
+        <v>0.2530802185727034</v>
       </c>
       <c r="Z36">
-        <v>0.360409176</v>
+        <v>0.3604091725433096</v>
       </c>
       <c r="AA36">
-        <v>0.06497631399999999</v>
+        <v>0.06497631337681108</v>
       </c>
       <c r="AB36">
-        <v>0.016294321</v>
+        <v>0.01629432084372089</v>
       </c>
       <c r="AC36">
-        <v>0.003068618</v>
+        <v>0.003068617970568833</v>
       </c>
       <c r="AD36">
-        <v>0.000174036</v>
+        <v>0.0001740359983308178</v>
       </c>
     </row>
     <row r="37">
@@ -4797,79 +5054,79 @@
         <v>14</v>
       </c>
       <c r="F37">
-        <v>1.45E-16</v>
+        <v>1.449999896719043E-16</v>
       </c>
       <c r="G37">
-        <v>5.819999999999999E-14</v>
+        <v>5.819999585451605E-14</v>
       </c>
       <c r="H37">
-        <v>8.93E-13</v>
+        <v>8.92999936393176E-13</v>
       </c>
       <c r="I37">
-        <v>1.23E-11</v>
+        <v>1.229999912389257E-11</v>
       </c>
       <c r="J37">
-        <v>1.45E-10</v>
+        <v>1.449999896719043E-10</v>
       </c>
       <c r="K37">
-        <v>1.47E-09</v>
+        <v>1.469999895294478E-09</v>
       </c>
       <c r="L37">
-        <v>1.27E-08</v>
+        <v>1.269999909540127E-08</v>
       </c>
       <c r="M37">
-        <v>9.49E-08</v>
+        <v>9.48999932404394E-08</v>
       </c>
       <c r="N37">
-        <v>6.03E-07</v>
+        <v>6.029999570493673E-07</v>
       </c>
       <c r="O37">
-        <v>3.31E-06</v>
+        <v>3.309999764234505E-06</v>
       </c>
       <c r="P37">
-        <v>1.56E-05</v>
+        <v>1.559999888883935E-05</v>
       </c>
       <c r="Q37">
-        <v>6.3E-05</v>
+        <v>6.299999551262047E-05</v>
       </c>
       <c r="R37">
-        <v>0.000219607</v>
+        <v>0.0002196069843577785</v>
       </c>
       <c r="S37">
-        <v>0.000979211</v>
+        <v>0.0009792109302525175</v>
       </c>
       <c r="T37">
-        <v>0.004388063</v>
+        <v>0.004388062687445967</v>
       </c>
       <c r="U37">
-        <v>0.013600209</v>
+        <v>0.01360020803128096</v>
       </c>
       <c r="V37">
-        <v>0.032737972</v>
+        <v>0.03273796966813166</v>
       </c>
       <c r="W37">
-        <v>0.066053133</v>
+        <v>0.06605312829515117</v>
       </c>
       <c r="X37">
-        <v>0.122041826</v>
+        <v>0.1220418173071747</v>
       </c>
       <c r="Y37">
-        <v>0.213152981</v>
+        <v>0.2131529658174869</v>
       </c>
       <c r="Z37">
-        <v>0.335523826</v>
+        <v>0.3355238021012262</v>
       </c>
       <c r="AA37">
-        <v>0.149232996</v>
+        <v>0.1492329853703954</v>
       </c>
       <c r="AB37">
-        <v>0.048517342</v>
+        <v>0.04851733854419481</v>
       </c>
       <c r="AC37">
-        <v>0.012385901</v>
+        <v>0.01238590011777399</v>
       </c>
       <c r="AD37">
-        <v>0.001084382</v>
+        <v>0.001084381922761372</v>
       </c>
     </row>
     <row r="38">
@@ -4891,79 +5148,79 @@
         <v>15</v>
       </c>
       <c r="F38">
-        <v>1.61E-16</v>
+        <v>1.60999994342187E-16</v>
       </c>
       <c r="G38">
-        <v>6.71E-14</v>
+        <v>6.70999976419922E-14</v>
       </c>
       <c r="H38">
-        <v>9.300000000000001E-13</v>
+        <v>9.299999673182229E-13</v>
       </c>
       <c r="I38">
-        <v>1.17E-11</v>
+        <v>1.169999958884216E-11</v>
       </c>
       <c r="J38">
-        <v>1.29E-10</v>
+        <v>1.289999954667212E-10</v>
       </c>
       <c r="K38">
-        <v>1.22E-09</v>
+        <v>1.219999957127131E-09</v>
       </c>
       <c r="L38">
-        <v>9.980000000000001E-09</v>
+        <v>9.979999649285877E-09</v>
       </c>
       <c r="M38">
-        <v>7.08E-08</v>
+        <v>7.079999751196793E-08</v>
       </c>
       <c r="N38">
-        <v>4.35E-07</v>
+        <v>4.349999847133623E-07</v>
       </c>
       <c r="O38">
-        <v>2.32E-06</v>
+        <v>2.319999918471266E-06</v>
       </c>
       <c r="P38">
-        <v>1.07E-05</v>
+        <v>1.069999962398385E-05</v>
       </c>
       <c r="Q38">
-        <v>4.3E-05</v>
+        <v>4.299999848890708E-05</v>
       </c>
       <c r="R38">
-        <v>0.000149742</v>
+        <v>0.0001497419947378122</v>
       </c>
       <c r="S38">
-        <v>0.000674638</v>
+        <v>0.0006746379762920765</v>
       </c>
       <c r="T38">
-        <v>0.003100028</v>
+        <v>0.003100027891059759</v>
       </c>
       <c r="U38">
-        <v>0.009952984</v>
+        <v>0.009952983650235264</v>
       </c>
       <c r="V38">
-        <v>0.024732098</v>
+        <v>0.02473209713087213</v>
       </c>
       <c r="W38">
-        <v>0.050485442</v>
+        <v>0.05048544022585595</v>
       </c>
       <c r="X38">
-        <v>0.092503064</v>
+        <v>0.09250306074928545</v>
       </c>
       <c r="Y38">
-        <v>0.162799267</v>
+        <v>0.1627992612789577</v>
       </c>
       <c r="Z38">
-        <v>0.2677573</v>
+        <v>0.2677572905905544</v>
       </c>
       <c r="AA38">
-        <v>0.250924142</v>
+        <v>0.2509241331821001</v>
       </c>
       <c r="AB38">
-        <v>0.100146381</v>
+        <v>0.1001463774806863</v>
       </c>
       <c r="AC38">
-        <v>0.032648451</v>
+        <v>0.03264844985267806</v>
       </c>
       <c r="AD38">
-        <v>0.004069961</v>
+        <v>0.004069960856974668</v>
       </c>
     </row>
     <row r="39">
@@ -4985,79 +5242,79 @@
         <v>16</v>
       </c>
       <c r="F39">
-        <v>3.23E-16</v>
+        <v>3.230000005438561E-16</v>
       </c>
       <c r="G39">
-        <v>7.59E-14</v>
+        <v>7.590000012779775E-14</v>
       </c>
       <c r="H39">
-        <v>9.590000000000001E-13</v>
+        <v>9.590000016147305E-13</v>
       </c>
       <c r="I39">
-        <v>1.12E-11</v>
+        <v>1.120000001885817E-11</v>
       </c>
       <c r="J39">
-        <v>1.14E-10</v>
+        <v>1.140000001919492E-10</v>
       </c>
       <c r="K39">
-        <v>1.02E-09</v>
+        <v>1.02000000171744E-09</v>
       </c>
       <c r="L39">
-        <v>7.87E-09</v>
+        <v>7.870000013251229E-09</v>
       </c>
       <c r="M39">
-        <v>5.33E-08</v>
+        <v>5.330000008974466E-08</v>
       </c>
       <c r="N39">
-        <v>3.15E-07</v>
+        <v>3.150000005303859E-07</v>
       </c>
       <c r="O39">
-        <v>1.63E-06</v>
+        <v>1.630000002744537E-06</v>
       </c>
       <c r="P39">
-        <v>7.37E-06</v>
+        <v>7.370000012409347E-06</v>
       </c>
       <c r="Q39">
-        <v>2.91E-05</v>
+        <v>2.910000004899756E-05</v>
       </c>
       <c r="R39">
-        <v>0.000100803</v>
+        <v>0.0001008030001697285</v>
       </c>
       <c r="S39">
-        <v>0.00045477</v>
+        <v>0.0004547700007657257</v>
       </c>
       <c r="T39">
-        <v>0.002119404</v>
+        <v>0.002119404003568578</v>
       </c>
       <c r="U39">
-        <v>0.006974726</v>
+        <v>0.006974726011743797</v>
       </c>
       <c r="V39">
-        <v>0.017801753</v>
+        <v>0.01780175302997396</v>
       </c>
       <c r="W39">
-        <v>0.036867265</v>
+        <v>0.03686726506207581</v>
       </c>
       <c r="X39">
-        <v>0.066992301</v>
+        <v>0.06699230111279929</v>
       </c>
       <c r="Y39">
-        <v>0.116373231</v>
+        <v>0.1163732311959451</v>
       </c>
       <c r="Z39">
-        <v>0.191698127</v>
+        <v>0.1916981273227746</v>
       </c>
       <c r="AA39">
-        <v>0.332021103</v>
+        <v>0.3320211035590454</v>
       </c>
       <c r="AB39">
-        <v>0.156109608</v>
+        <v>0.1561096082628519</v>
       </c>
       <c r="AC39">
-        <v>0.062078414</v>
+        <v>0.06207841410452545</v>
       </c>
       <c r="AD39">
-        <v>0.010370016</v>
+        <v>0.01037001601746067</v>
       </c>
     </row>
     <row r="40">
@@ -5079,79 +5336,79 @@
         <v>17</v>
       </c>
       <c r="F40">
-        <v>3.04E-16</v>
+        <v>3.040000219904536E-16</v>
       </c>
       <c r="G40">
-        <v>8.65E-14</v>
+        <v>8.650000625715209E-14</v>
       </c>
       <c r="H40">
-        <v>1E-12</v>
+        <v>1.000000072337018E-12</v>
       </c>
       <c r="I40">
-        <v>1.09E-11</v>
+        <v>1.09000007884735E-11</v>
       </c>
       <c r="J40">
-        <v>1.04E-10</v>
+        <v>1.040000075230499E-10</v>
       </c>
       <c r="K40">
-        <v>8.67E-10</v>
+        <v>8.670000627161949E-10</v>
       </c>
       <c r="L40">
-        <v>6.38E-09</v>
+        <v>6.380000461510177E-09</v>
       </c>
       <c r="M40">
-        <v>4.13E-08</v>
+        <v>4.130000298751886E-08</v>
       </c>
       <c r="N40">
-        <v>2.35E-07</v>
+        <v>2.350000169991993E-07</v>
       </c>
       <c r="O40">
-        <v>1.17E-06</v>
+        <v>1.170000084634312E-06</v>
       </c>
       <c r="P40">
-        <v>5.21E-06</v>
+        <v>5.210000376875866E-06</v>
       </c>
       <c r="Q40">
-        <v>2.01E-05</v>
+        <v>2.010000145397407E-05</v>
       </c>
       <c r="R40">
-        <v>6.889999999999999E-05</v>
+        <v>6.890000498402056E-05</v>
       </c>
       <c r="S40">
-        <v>0.000309476</v>
+        <v>0.0003094760223865711</v>
       </c>
       <c r="T40">
-        <v>0.001449757</v>
+        <v>0.001449757104871099</v>
       </c>
       <c r="U40">
-        <v>0.00484643</v>
+        <v>0.004846430350576296</v>
       </c>
       <c r="V40">
-        <v>0.012628723</v>
+        <v>0.01262872391352417</v>
       </c>
       <c r="W40">
-        <v>0.026546414</v>
+        <v>0.02654641592028844</v>
       </c>
       <c r="X40">
-        <v>0.048046041</v>
+        <v>0.04804604447550735</v>
       </c>
       <c r="Y40">
-        <v>0.081842153</v>
+        <v>0.08184215892021733</v>
       </c>
       <c r="Z40">
-        <v>0.131223121</v>
+        <v>0.1312231304922893</v>
       </c>
       <c r="AA40">
-        <v>0.376335348</v>
+        <v>0.376335375222977</v>
       </c>
       <c r="AB40">
-        <v>0.2019657</v>
+        <v>0.2019657146095966</v>
       </c>
       <c r="AC40">
-        <v>0.0945217</v>
+        <v>0.09452170683741795</v>
       </c>
       <c r="AD40">
-        <v>0.020189401</v>
+        <v>0.02018940246044107</v>
       </c>
     </row>
     <row r="41">
@@ -5173,79 +5430,79 @@
         <v>18</v>
       </c>
       <c r="F41">
-        <v>4.2E-16</v>
+        <v>4.199999958351198E-16</v>
       </c>
       <c r="G41">
-        <v>1.01E-13</v>
+        <v>1.009999989984455E-13</v>
       </c>
       <c r="H41">
-        <v>1.08E-12</v>
+        <v>1.079999989290308E-12</v>
       </c>
       <c r="I41">
-        <v>1.09E-11</v>
+        <v>1.089999989191144E-11</v>
       </c>
       <c r="J41">
-        <v>9.83E-11</v>
+        <v>9.829999902521971E-11</v>
       </c>
       <c r="K41">
-        <v>7.76E-10</v>
+        <v>7.759999923048881E-10</v>
       </c>
       <c r="L41">
-        <v>5.43E-09</v>
+        <v>5.429999946154049E-09</v>
       </c>
       <c r="M41">
-        <v>3.36E-08</v>
+        <v>3.359999966680959E-08</v>
       </c>
       <c r="N41">
-        <v>1.84E-07</v>
+        <v>1.839999981753858E-07</v>
       </c>
       <c r="O41">
-        <v>8.92E-07</v>
+        <v>8.919999911545878E-07</v>
       </c>
       <c r="P41">
-        <v>3.84E-06</v>
+        <v>3.839999961921095E-06</v>
       </c>
       <c r="Q41">
-        <v>1.46E-05</v>
+        <v>1.459999985522083E-05</v>
       </c>
       <c r="R41">
-        <v>4.92E-05</v>
+        <v>4.919999951211404E-05</v>
       </c>
       <c r="S41">
-        <v>0.000218751</v>
+        <v>0.0002187509978307817</v>
       </c>
       <c r="T41">
-        <v>0.00102309</v>
+        <v>0.001023089989854649</v>
       </c>
       <c r="U41">
-        <v>0.003448521</v>
+        <v>0.003448520965803151</v>
       </c>
       <c r="V41">
-        <v>0.009118828000000001</v>
+        <v>0.009118827909574224</v>
       </c>
       <c r="W41">
-        <v>0.019425618</v>
+        <v>0.01942561780736816</v>
       </c>
       <c r="X41">
-        <v>0.035157333</v>
+        <v>0.03515733265136647</v>
       </c>
       <c r="Y41">
-        <v>0.05878545</v>
+        <v>0.05878544941706106</v>
       </c>
       <c r="Z41">
-        <v>0.090268917</v>
+        <v>0.090268916104859</v>
       </c>
       <c r="AA41">
-        <v>0.390873316</v>
+        <v>0.3908733121239512</v>
       </c>
       <c r="AB41">
-        <v>0.23360726</v>
+        <v>0.2336072576834613</v>
       </c>
       <c r="AC41">
-        <v>0.125082182</v>
+        <v>0.1250821807596374</v>
       </c>
       <c r="AD41">
-        <v>0.032921988</v>
+        <v>0.03292198767353301</v>
       </c>
     </row>
     <row r="42">
@@ -5267,79 +5524,79 @@
         <v>19</v>
       </c>
       <c r="F42">
-        <v>6.44E-16</v>
+        <v>6.439999692523867E-16</v>
       </c>
       <c r="G42">
-        <v>1.23E-13</v>
+        <v>1.229999941273968E-13</v>
       </c>
       <c r="H42">
-        <v>1.22E-12</v>
+        <v>1.219999941751416E-12</v>
       </c>
       <c r="I42">
-        <v>1.16E-11</v>
+        <v>1.1599999446161E-11</v>
       </c>
       <c r="J42">
-        <v>9.78E-11</v>
+        <v>9.779999533056431E-11</v>
       </c>
       <c r="K42">
-        <v>7.340000000000001E-10</v>
+        <v>7.3399996495536E-10</v>
       </c>
       <c r="L42">
-        <v>4.9E-09</v>
+        <v>4.899999766050768E-09</v>
       </c>
       <c r="M42">
-        <v>2.9E-08</v>
+        <v>2.899999861540251E-08</v>
       </c>
       <c r="N42">
-        <v>1.53E-07</v>
+        <v>1.529999926950546E-07</v>
       </c>
       <c r="O42">
-        <v>7.180000000000001E-07</v>
+        <v>7.179999657192758E-07</v>
       </c>
       <c r="P42">
-        <v>3.01E-06</v>
+        <v>3.009999856288329E-06</v>
       </c>
       <c r="Q42">
-        <v>1.12E-05</v>
+        <v>1.11999994652589E-05</v>
       </c>
       <c r="R42">
-        <v>3.71E-05</v>
+        <v>3.70999982286701E-05</v>
       </c>
       <c r="S42">
-        <v>0.00016277</v>
+        <v>0.0001627699922285885</v>
       </c>
       <c r="T42">
-        <v>0.000756072</v>
+        <v>0.000756071963901538</v>
       </c>
       <c r="U42">
-        <v>0.002553929</v>
+        <v>0.002553928878063321</v>
       </c>
       <c r="V42">
-        <v>0.006815917</v>
+        <v>0.006815916674575807</v>
       </c>
       <c r="W42">
-        <v>0.014675336</v>
+        <v>0.01467533529932988</v>
       </c>
       <c r="X42">
-        <v>0.026620559</v>
+        <v>0.0266205577290083</v>
       </c>
       <c r="Y42">
-        <v>0.043858689</v>
+        <v>0.04385868690597824</v>
       </c>
       <c r="Z42">
-        <v>0.06408119900000001</v>
+        <v>0.06408119594045975</v>
       </c>
       <c r="AA42">
-        <v>0.3878605</v>
+        <v>0.3878604814817008</v>
       </c>
       <c r="AB42">
-        <v>0.253190793</v>
+        <v>0.2531907809114711</v>
       </c>
       <c r="AC42">
-        <v>0.151631719</v>
+        <v>0.1516317117603828</v>
       </c>
       <c r="AD42">
-        <v>0.047740349</v>
+        <v>0.04774034672064939</v>
       </c>
     </row>
     <row r="43">
@@ -5361,79 +5618,79 @@
         <v>20</v>
       </c>
       <c r="F43">
-        <v>9.549999999999999E-16</v>
+        <v>9.549999645461067E-16</v>
       </c>
       <c r="G43">
-        <v>1.56E-13</v>
+        <v>1.559999942085787E-13</v>
       </c>
       <c r="H43">
-        <v>1.44E-12</v>
+        <v>1.439999946540727E-12</v>
       </c>
       <c r="I43">
-        <v>1.29E-11</v>
+        <v>1.289999952109401E-11</v>
       </c>
       <c r="J43">
-        <v>1.03E-10</v>
+        <v>1.02999996176177E-10</v>
       </c>
       <c r="K43">
-        <v>7.37E-10</v>
+        <v>7.369999726392469E-10</v>
       </c>
       <c r="L43">
-        <v>4.67E-09</v>
+        <v>4.669999826628606E-09</v>
       </c>
       <c r="M43">
-        <v>2.66E-08</v>
+        <v>2.659999901248842E-08</v>
       </c>
       <c r="N43">
-        <v>1.35E-07</v>
+        <v>1.349999949881931E-07</v>
       </c>
       <c r="O43">
-        <v>6.16E-07</v>
+        <v>6.159999771313108E-07</v>
       </c>
       <c r="P43">
-        <v>2.49E-06</v>
+        <v>2.489999907560006E-06</v>
       </c>
       <c r="Q43">
-        <v>9.07E-06</v>
+        <v>9.069999663280827E-06</v>
       </c>
       <c r="R43">
-        <v>2.96E-05</v>
+        <v>2.959999890111494E-05</v>
       </c>
       <c r="S43">
-        <v>0.000127693</v>
+        <v>0.0001276929952594618</v>
       </c>
       <c r="T43">
-        <v>0.00058676</v>
+        <v>0.0005867599782168311</v>
       </c>
       <c r="U43">
-        <v>0.001976911</v>
+        <v>0.001976910926608177</v>
       </c>
       <c r="V43">
-        <v>0.005300077</v>
+        <v>0.005300076803237316</v>
       </c>
       <c r="W43">
-        <v>0.011498489</v>
+        <v>0.0114984885731244</v>
       </c>
       <c r="X43">
-        <v>0.020920993</v>
+        <v>0.02092099222331869</v>
       </c>
       <c r="Y43">
-        <v>0.034098762</v>
+        <v>0.03409876073410066</v>
       </c>
       <c r="Z43">
-        <v>0.047404616</v>
+        <v>0.04740461424012755</v>
       </c>
       <c r="AA43">
-        <v>0.37626103</v>
+        <v>0.3762610160314991</v>
       </c>
       <c r="AB43">
-        <v>0.264162793</v>
+        <v>0.2641627831930896</v>
       </c>
       <c r="AC43">
-        <v>0.173748791</v>
+        <v>0.1737487845496638</v>
       </c>
       <c r="AD43">
-        <v>0.063871179</v>
+        <v>0.06387117662881471</v>
       </c>
     </row>
     <row r="44">
@@ -5455,79 +5712,79 @@
         <v>21</v>
       </c>
       <c r="F44">
-        <v>1.45E-15</v>
+        <v>1.449999963508045E-15</v>
       </c>
       <c r="G44">
-        <v>2.05E-13</v>
+        <v>2.049999948407925E-13</v>
       </c>
       <c r="H44">
-        <v>1.76E-12</v>
+        <v>1.759999955706316E-12</v>
       </c>
       <c r="I44">
-        <v>1.49E-11</v>
+        <v>1.48999996250137E-11</v>
       </c>
       <c r="J44">
-        <v>1.13E-10</v>
+        <v>1.129999971561442E-10</v>
       </c>
       <c r="K44">
-        <v>7.67E-10</v>
+        <v>7.66999980697014E-10</v>
       </c>
       <c r="L44">
-        <v>4.67E-09</v>
+        <v>4.669999882470736E-09</v>
       </c>
       <c r="M44">
-        <v>2.56E-08</v>
+        <v>2.559999935572824E-08</v>
       </c>
       <c r="N44">
-        <v>1.25E-07</v>
+        <v>1.249999968541418E-07</v>
       </c>
       <c r="O44">
-        <v>5.51E-07</v>
+        <v>5.50999986133057E-07</v>
       </c>
       <c r="P44">
-        <v>2.18E-06</v>
+        <v>2.179999945136233E-06</v>
       </c>
       <c r="Q44">
-        <v>7.77E-06</v>
+        <v>7.769999804453454E-06</v>
       </c>
       <c r="R44">
-        <v>2.48E-05</v>
+        <v>2.479999937586173E-05</v>
       </c>
       <c r="S44">
-        <v>0.000105218</v>
+        <v>0.0001052179973519927</v>
       </c>
       <c r="T44">
-        <v>0.000476929</v>
+        <v>0.0004769289879971919</v>
       </c>
       <c r="U44">
-        <v>0.00159667</v>
+        <v>0.00159666995981682</v>
       </c>
       <c r="V44">
-        <v>0.004282818</v>
+        <v>0.004282817892214894</v>
       </c>
       <c r="W44">
-        <v>0.009333919</v>
+        <v>0.009333918765094514</v>
       </c>
       <c r="X44">
-        <v>0.017028656</v>
+        <v>0.0170286555714421</v>
       </c>
       <c r="Y44">
-        <v>0.027544158</v>
+        <v>0.02754415730679987</v>
       </c>
       <c r="Z44">
-        <v>0.036570206</v>
+        <v>0.03657020507964254</v>
       </c>
       <c r="AA44">
-        <v>0.3612362</v>
+        <v>0.3612361909088171</v>
       </c>
       <c r="AB44">
-        <v>0.269392913</v>
+        <v>0.2693929062202247</v>
       </c>
       <c r="AC44">
-        <v>0.191733386</v>
+        <v>0.1917333811746716</v>
       </c>
       <c r="AD44">
-        <v>0.080663495</v>
+        <v>0.08066349296995265</v>
       </c>
     </row>
   </sheetData>
@@ -16891,7 +17148,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Diet_loglike</t>
+          <t>Diet_distribution</t>
         </is>
       </c>
       <c r="B14">
@@ -82955,7 +83212,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sigma_rec_prior</t>
+          <t>sigma_rec</t>
         </is>
       </c>
       <c r="B16">
@@ -83068,7 +83325,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Time_varying_sel_sd_prior</t>
+          <t>Time_varying_sel_sd</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -83078,17 +83335,17 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Sel_norm_bin1</t>
+          <t>Sel_norm_bin</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Sel_norm_bin2</t>
+          <t>Sel_norm_bin_upper</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Comp_loglike</t>
+          <t>Comp_distribution</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -83098,12 +83355,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CAAL_loglike</t>
+          <t>CAAL_distribution</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Weight1_Numbers2</t>
+          <t>Observation_units</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -83118,7 +83375,7 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Q_index</t>
+          <t>Catchability_index</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -83128,12 +83385,12 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Q_prior</t>
+          <t>Catchability_init</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Q_sd_prior</t>
+          <t>Catchability_prior_sd</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -83143,7 +83400,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Time_varying_q_sd_prior</t>
+          <t>Time_varying_q_sd</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
@@ -83153,7 +83410,7 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Index_sd_prior</t>
+          <t>Index_sd</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -83163,12 +83420,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Catch_sd_prior</t>
+          <t>Catch_sd</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>proj_F_prop</t>
+          <t>Proj_F_proportion</t>
         </is>
       </c>
     </row>
@@ -83692,7 +83949,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -83723,20 +83980,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Selectivity_block</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Q_block</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Log_sd</t>
         </is>
@@ -83761,15 +84008,9 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2912869.455</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2912869.455</v>
-      </c>
-      <c r="I2">
         <v>0.1253784029181239</v>
       </c>
     </row>
@@ -83792,15 +84033,9 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5921380.162</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>5921380.162</v>
-      </c>
-      <c r="I3">
         <v>0.08414600237513743</v>
       </c>
     </row>
@@ -83823,15 +84058,9 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4542404.99</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>4542404.99</v>
-      </c>
-      <c r="I4">
         <v>0.1019185434683115</v>
       </c>
     </row>
@@ -83854,15 +84083,9 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>5949852.335</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>5949852.335</v>
-      </c>
-      <c r="I5">
         <v>0.07016891044639602</v>
       </c>
     </row>
@@ -83885,15 +84108,9 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4835722.134</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>4835722.134</v>
-      </c>
-      <c r="I6">
         <v>0.09862713128764673</v>
       </c>
     </row>
@@ -83916,15 +84133,9 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>5498433.45</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5498433.45</v>
-      </c>
-      <c r="I7">
         <v>0.110720119948757</v>
       </c>
     </row>
@@ -83947,15 +84158,9 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>7183962.71</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>7183962.71</v>
-      </c>
-      <c r="I8">
         <v>0.1037931162391902</v>
       </c>
     </row>
@@ -83978,15 +84183,9 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>6550414.87</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>6550414.87</v>
-      </c>
-      <c r="I9">
         <v>0.09211958435883832</v>
       </c>
     </row>
@@ -84009,15 +84208,9 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>7296652.94</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>7296652.94</v>
-      </c>
-      <c r="I10">
         <v>0.13094131090379</v>
       </c>
     </row>
@@ -84040,15 +84233,9 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>5129537.61</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>5129537.61</v>
-      </c>
-      <c r="I11">
         <v>0.1243944924983529</v>
       </c>
     </row>
@@ -84071,15 +84258,9 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4526153.25</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>4526153.25</v>
-      </c>
-      <c r="I12">
         <v>0.1130566779878027</v>
       </c>
     </row>
@@ -84102,15 +84283,9 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>5294816.27</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>5294816.27</v>
-      </c>
-      <c r="I13">
         <v>0.08865581616426742</v>
       </c>
     </row>
@@ -84133,15 +84308,9 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>5027325.31</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>5027325.31</v>
-      </c>
-      <c r="I14">
         <v>0.1045522811379963</v>
       </c>
     </row>
@@ -84164,15 +84333,9 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>5477837.81</v>
       </c>
       <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>5477837.81</v>
-      </c>
-      <c r="I15">
         <v>0.1879604462575741</v>
       </c>
     </row>
@@ -84195,15 +84358,9 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3125253.08</v>
       </c>
       <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>3125253.08</v>
-      </c>
-      <c r="I16">
         <v>0.08846227830955401</v>
       </c>
     </row>
@@ -84226,15 +84383,9 @@
         <v>6</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>3562163.12</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>3562163.12</v>
-      </c>
-      <c r="I17">
         <v>0.1182665156463772</v>
       </c>
     </row>
@@ -84257,15 +84408,9 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2687755.27</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>2687755.27</v>
-      </c>
-      <c r="I18">
         <v>0.1092525699096841</v>
       </c>
     </row>
@@ -84288,15 +84433,9 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>3798474.08</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>3798474.08</v>
-      </c>
-      <c r="I19">
         <v>0.1176509494452982</v>
       </c>
     </row>
@@ -84319,15 +84458,9 @@
         <v>6</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>5103629.01</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>5103629.01</v>
-      </c>
-      <c r="I20">
         <v>0.1123323579203355</v>
       </c>
     </row>
@@ -84350,15 +84483,9 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4196853.9</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>4196853.9</v>
-      </c>
-      <c r="I21">
         <v>0.08086190826834753</v>
       </c>
     </row>
@@ -84381,15 +84508,9 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>4953438.27</v>
       </c>
       <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>4953438.27</v>
-      </c>
-      <c r="I22">
         <v>0.09057702535294569</v>
       </c>
     </row>
@@ -84412,15 +84533,9 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>8392260.85</v>
       </c>
       <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>8392260.85</v>
-      </c>
-      <c r="I23">
         <v>0.2388069692780838</v>
       </c>
     </row>
@@ -84443,15 +84558,9 @@
         <v>6</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>3862974.16</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>3862974.16</v>
-      </c>
-      <c r="I24">
         <v>0.09226814021133964</v>
       </c>
     </row>
@@ -84474,15 +84583,9 @@
         <v>6</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>4868615.63</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>4868615.63</v>
-      </c>
-      <c r="I25">
         <v>0.09254512816047421</v>
       </c>
     </row>
@@ -84505,15 +84608,9 @@
         <v>6</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3045380.11</v>
       </c>
       <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>3045380.11</v>
-      </c>
-      <c r="I26">
         <v>0.0929886551236664</v>
       </c>
     </row>
@@ -84536,15 +84633,9 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>4338219.9</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>4338219.9</v>
-      </c>
-      <c r="I27">
         <v>0.1028399651231192</v>
       </c>
     </row>
@@ -84567,15 +84658,9 @@
         <v>6</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>3023267.26</v>
       </c>
       <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>3023267.26</v>
-      </c>
-      <c r="I28">
         <v>0.113926925375199</v>
       </c>
     </row>
@@ -84598,15 +84683,9 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2282409.6</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>2282409.6</v>
-      </c>
-      <c r="I29">
         <v>0.1209296201234053</v>
       </c>
     </row>
@@ -84629,15 +84708,9 @@
         <v>6</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>3737878.33</v>
       </c>
       <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <v>3737878.33</v>
-      </c>
-      <c r="I30">
         <v>0.1144674372937692</v>
       </c>
     </row>
@@ -84660,15 +84733,9 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3112312.23</v>
       </c>
       <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31">
-        <v>3112312.23</v>
-      </c>
-      <c r="I31">
         <v>0.09067831135711464</v>
       </c>
     </row>
@@ -84691,15 +84758,9 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>3487228.58</v>
       </c>
       <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32">
-        <v>3487228.58</v>
-      </c>
-      <c r="I32">
         <v>0.09831751860005575</v>
       </c>
     </row>
@@ -84722,15 +84783,9 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>4575402.88</v>
       </c>
       <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <v>4575402.88</v>
-      </c>
-      <c r="I33">
         <v>0.0799104970263768</v>
       </c>
     </row>
@@ -84753,15 +84808,9 @@
         <v>6</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>7429952.48</v>
       </c>
       <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <v>7429952.48</v>
-      </c>
-      <c r="I34">
         <v>0.06519684224855118</v>
       </c>
     </row>
@@ -84784,15 +84833,9 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>6394358.6</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>6394358.6</v>
-      </c>
-      <c r="I35">
         <v>0.06286350469717354</v>
       </c>
     </row>
@@ -84815,15 +84858,9 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>4910079.82</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>4910079.82</v>
-      </c>
-      <c r="I36">
         <v>0.09125992451247497</v>
       </c>
     </row>
@@ -84846,15 +84883,9 @@
         <v>6</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>4814372.77</v>
       </c>
       <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37">
-        <v>4814372.77</v>
-      </c>
-      <c r="I37">
         <v>0.07458844358146308</v>
       </c>
     </row>
@@ -84877,15 +84908,9 @@
         <v>6</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>1093495.49</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <v>1093495.49</v>
-      </c>
-      <c r="I38">
         <v>0.06747681820768542</v>
       </c>
     </row>
@@ -84908,15 +84933,9 @@
         <v>6</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>1262727.12</v>
       </c>
       <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <v>1262727.12</v>
-      </c>
-      <c r="I39">
         <v>0.09557261835177058</v>
       </c>
     </row>
@@ -84939,15 +84958,9 @@
         <v>6</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>1078132.1</v>
       </c>
       <c r="G40">
-        <v>1</v>
-      </c>
-      <c r="H40">
-        <v>1078132.1</v>
-      </c>
-      <c r="I40">
         <v>0.05793421301747003</v>
       </c>
     </row>
@@ -84970,15 +84983,9 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>1114623.86</v>
       </c>
       <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>1114623.86</v>
-      </c>
-      <c r="I41">
         <v>0.05473413462499146</v>
       </c>
     </row>
@@ -85001,15 +85008,9 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>1189234.46</v>
       </c>
       <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>1189234.46</v>
-      </c>
-      <c r="I42">
         <v>0.05849707555563897</v>
       </c>
     </row>
@@ -85032,15 +85033,9 @@
         <v>6</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>1064599.55</v>
       </c>
       <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>1064599.55</v>
-      </c>
-      <c r="I43">
         <v>0.06006010760627037</v>
       </c>
     </row>
@@ -85063,15 +85058,9 @@
         <v>6</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>976152.25</v>
       </c>
       <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>976152.25</v>
-      </c>
-      <c r="I44">
         <v>0.07925850446149192</v>
       </c>
     </row>
@@ -85094,15 +85083,9 @@
         <v>6</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>868804.01</v>
       </c>
       <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>868804.01</v>
-      </c>
-      <c r="I45">
         <v>0.0722845482480045</v>
       </c>
     </row>
@@ -85125,15 +85108,9 @@
         <v>6</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>728995.97</v>
       </c>
       <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>728995.97</v>
-      </c>
-      <c r="I46">
         <v>0.07231933563982726</v>
       </c>
     </row>
@@ -85156,15 +85133,9 @@
         <v>6</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>530488.23</v>
       </c>
       <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47">
-        <v>530488.23</v>
-      </c>
-      <c r="I47">
         <v>0.07222885144309277</v>
       </c>
     </row>
@@ -85187,15 +85158,9 @@
         <v>6</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>538861.85</v>
       </c>
       <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48">
-        <v>538861.85</v>
-      </c>
-      <c r="I48">
         <v>0.08276221116539087</v>
       </c>
     </row>
@@ -85218,15 +85183,9 @@
         <v>6</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>669305.12</v>
       </c>
       <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>669305.12</v>
-      </c>
-      <c r="I49">
         <v>0.0792877437527041</v>
       </c>
     </row>
@@ -85249,15 +85208,9 @@
         <v>6</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>1377095.01</v>
       </c>
       <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>1377095.01</v>
-      </c>
-      <c r="I50">
         <v>0.1784869913424109</v>
       </c>
     </row>
@@ -85280,15 +85233,9 @@
         <v>6</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>1008292.93</v>
       </c>
       <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="H51">
-        <v>1008292.93</v>
-      </c>
-      <c r="I51">
         <v>0.09069601678919928</v>
       </c>
     </row>
@@ -85311,15 +85258,9 @@
         <v>6</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>909133.03</v>
       </c>
       <c r="G52">
-        <v>1</v>
-      </c>
-      <c r="H52">
-        <v>909133.03</v>
-      </c>
-      <c r="I52">
         <v>0.09610419603390975</v>
       </c>
     </row>
@@ -85342,15 +85283,9 @@
         <v>6</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>627150.55</v>
       </c>
       <c r="G53">
-        <v>1</v>
-      </c>
-      <c r="H53">
-        <v>627150.55</v>
-      </c>
-      <c r="I53">
         <v>0.10876005261786</v>
       </c>
     </row>
@@ -85373,15 +85308,9 @@
         <v>6</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>550504.25</v>
       </c>
       <c r="G54">
-        <v>1</v>
-      </c>
-      <c r="H54">
-        <v>550504.25</v>
-      </c>
-      <c r="I54">
         <v>0.07801549466316546</v>
       </c>
     </row>
@@ -85404,15 +85333,9 @@
         <v>6</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>618678.61</v>
       </c>
       <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <v>618678.61</v>
-      </c>
-      <c r="I55">
         <v>0.09125807535697056</v>
       </c>
     </row>
@@ -85435,15 +85358,9 @@
         <v>6</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>537562.71</v>
       </c>
       <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56">
-        <v>537562.71</v>
-      </c>
-      <c r="I56">
         <v>0.08018159310985948</v>
       </c>
     </row>
@@ -85466,15 +85383,9 @@
         <v>6</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>827176.15</v>
       </c>
       <c r="G57">
-        <v>1</v>
-      </c>
-      <c r="H57">
-        <v>827176.15</v>
-      </c>
-      <c r="I57">
         <v>0.08848481360692215</v>
       </c>
     </row>
@@ -85497,15 +85408,9 @@
         <v>6</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>597943.34</v>
       </c>
       <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58">
-        <v>597943.34</v>
-      </c>
-      <c r="I58">
         <v>0.1064717232735053</v>
       </c>
     </row>
@@ -85528,15 +85433,9 @@
         <v>6</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>625659.39</v>
       </c>
       <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <v>625659.39</v>
-      </c>
-      <c r="I59">
         <v>0.09949214263021464</v>
       </c>
     </row>
@@ -85559,15 +85458,9 @@
         <v>6</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>578064.11</v>
       </c>
       <c r="G60">
-        <v>1</v>
-      </c>
-      <c r="H60">
-        <v>578064.11</v>
-      </c>
-      <c r="I60">
         <v>0.05847806826272353</v>
       </c>
     </row>
@@ -85590,15 +85483,9 @@
         <v>6</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>638763.99</v>
       </c>
       <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>638763.99</v>
-      </c>
-      <c r="I61">
         <v>0.06797489788314393</v>
       </c>
     </row>
@@ -85621,15 +85508,9 @@
         <v>6</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>544035.14</v>
       </c>
       <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62">
-        <v>544035.14</v>
-      </c>
-      <c r="I62">
         <v>0.05320268752854448</v>
       </c>
     </row>
@@ -85652,15 +85533,9 @@
         <v>6</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>450337.12</v>
       </c>
       <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63">
-        <v>450337.12</v>
-      </c>
-      <c r="I63">
         <v>0.07778718216437483</v>
       </c>
     </row>
@@ -85683,15 +85558,9 @@
         <v>6</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>427503.06</v>
       </c>
       <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64">
-        <v>427503.06</v>
-      </c>
-      <c r="I64">
         <v>0.06507070747701725</v>
       </c>
     </row>
@@ -85714,15 +85583,9 @@
         <v>6</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>430084.42</v>
       </c>
       <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65">
-        <v>430084.42</v>
-      </c>
-      <c r="I65">
         <v>0.08138629281366894</v>
       </c>
     </row>
@@ -85745,15 +85608,9 @@
         <v>6</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>870638.63</v>
       </c>
       <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66">
-        <v>870638.63</v>
-      </c>
-      <c r="I66">
         <v>0.1171543791723795</v>
       </c>
     </row>
@@ -85776,15 +85633,9 @@
         <v>6</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>911081.9300000001</v>
       </c>
       <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <v>911081.9300000001</v>
-      </c>
-      <c r="I67">
         <v>0.07335167999603075</v>
       </c>
     </row>
@@ -85807,15 +85658,9 @@
         <v>6</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>896401.0699999999</v>
       </c>
       <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68">
-        <v>896401.0699999999</v>
-      </c>
-      <c r="I68">
         <v>0.1117503487285052</v>
       </c>
     </row>
@@ -85838,15 +85683,9 @@
         <v>6</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>811666.6899999999</v>
       </c>
       <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69">
-        <v>811666.6899999999</v>
-      </c>
-      <c r="I69">
         <v>0.09123096445321267</v>
       </c>
     </row>
@@ -85869,15 +85708,9 @@
         <v>6</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>1095269.92</v>
       </c>
       <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <v>1095269.92</v>
-      </c>
-      <c r="I70">
         <v>0.1393299217978832</v>
       </c>
     </row>
@@ -85900,15 +85733,9 @@
         <v>6</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>1109115.19</v>
       </c>
       <c r="G71">
-        <v>1</v>
-      </c>
-      <c r="H71">
-        <v>1109115.19</v>
-      </c>
-      <c r="I71">
         <v>0.1355145973579677</v>
       </c>
     </row>
@@ -85931,15 +85758,9 @@
         <v>6</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>986012.89</v>
       </c>
       <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <v>986012.89</v>
-      </c>
-      <c r="I72">
         <v>0.07835833680297435</v>
       </c>
     </row>
@@ -85962,15 +85783,9 @@
         <v>6</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>643952.5600000001</v>
       </c>
       <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="H73">
-        <v>643952.5600000001</v>
-      </c>
-      <c r="I73">
         <v>0.07749177856883857</v>
       </c>
     </row>
@@ -85993,15 +85808,9 @@
         <v>6</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>69990</v>
       </c>
       <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>69990</v>
-      </c>
-      <c r="I74">
         <v>0.1085662889974727</v>
       </c>
     </row>
@@ -86024,15 +85833,9 @@
         <v>6</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>110643</v>
       </c>
       <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <v>110643</v>
-      </c>
-      <c r="I75">
         <v>0.09228977976064298</v>
       </c>
     </row>
@@ -86055,15 +85858,9 @@
         <v>6</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>160396</v>
       </c>
       <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="H76">
-        <v>160396</v>
-      </c>
-      <c r="I76">
         <v>0.1429792055649829</v>
       </c>
     </row>
@@ -86086,15 +85883,9 @@
         <v>6</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>163637</v>
       </c>
       <c r="G77">
-        <v>1</v>
-      </c>
-      <c r="H77">
-        <v>163637</v>
-      </c>
-      <c r="I77">
         <v>0.08982261502285643</v>
       </c>
     </row>
@@ -86117,15 +85908,9 @@
         <v>6</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>229865</v>
       </c>
       <c r="G78">
-        <v>1</v>
-      </c>
-      <c r="H78">
-        <v>229865</v>
-      </c>
-      <c r="I78">
         <v>0.1017913073770974</v>
       </c>
     </row>
@@ -86148,15 +85933,9 @@
         <v>6</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>280116.93</v>
       </c>
       <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <v>280116.93</v>
-      </c>
-      <c r="I79">
         <v>0.07131919947205936</v>
       </c>
     </row>
@@ -86179,15 +85958,9 @@
         <v>6</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>297331.22</v>
       </c>
       <c r="G80">
-        <v>1</v>
-      </c>
-      <c r="H80">
-        <v>297331.22</v>
-      </c>
-      <c r="I80">
         <v>0.1176926771296291</v>
       </c>
     </row>
@@ -86210,15 +85983,9 @@
         <v>6</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>339246.36</v>
       </c>
       <c r="G81">
-        <v>1</v>
-      </c>
-      <c r="H81">
-        <v>339246.36</v>
-      </c>
-      <c r="I81">
         <v>0.1041140649046111</v>
       </c>
     </row>
@@ -86241,15 +86008,9 @@
         <v>6</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>402326.27</v>
       </c>
       <c r="G82">
-        <v>1</v>
-      </c>
-      <c r="H82">
-        <v>402326.27</v>
-      </c>
-      <c r="I82">
         <v>0.08982820218681244</v>
       </c>
     </row>
@@ -86272,15 +86033,9 @@
         <v>6</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>298788.7</v>
       </c>
       <c r="G83">
-        <v>1</v>
-      </c>
-      <c r="H83">
-        <v>298788.7</v>
-      </c>
-      <c r="I83">
         <v>0.1261991044529835</v>
       </c>
     </row>
@@ -86303,15 +86058,9 @@
         <v>6</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>345561.59</v>
       </c>
       <c r="G84">
-        <v>1</v>
-      </c>
-      <c r="H84">
-        <v>345561.59</v>
-      </c>
-      <c r="I84">
         <v>0.1393033146282224</v>
       </c>
     </row>
@@ -86334,15 +86083,9 @@
         <v>6</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>446816.06</v>
       </c>
       <c r="G85">
-        <v>1</v>
-      </c>
-      <c r="H85">
-        <v>446816.06</v>
-      </c>
-      <c r="I85">
         <v>0.09465233617142117</v>
       </c>
     </row>
@@ -86365,15 +86108,9 @@
         <v>6</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>476355.38</v>
       </c>
       <c r="G86">
-        <v>1</v>
-      </c>
-      <c r="H86">
-        <v>476355.38</v>
-      </c>
-      <c r="I86">
         <v>0.09764102716059268</v>
       </c>
     </row>
@@ -86396,15 +86133,9 @@
         <v>6</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>448016.2</v>
       </c>
       <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <v>448016.2</v>
-      </c>
-      <c r="I87">
         <v>0.1446514015785237</v>
       </c>
     </row>
@@ -86427,15 +86158,9 @@
         <v>6</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>527254.48</v>
       </c>
       <c r="G88">
-        <v>1</v>
-      </c>
-      <c r="H88">
-        <v>527254.48</v>
-      </c>
-      <c r="I88">
         <v>0.1048840949786418</v>
       </c>
     </row>
@@ -86458,15 +86183,9 @@
         <v>6</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>463080.74</v>
       </c>
       <c r="G89">
-        <v>1</v>
-      </c>
-      <c r="H89">
-        <v>463080.74</v>
-      </c>
-      <c r="I89">
         <v>0.1278410524950195</v>
       </c>
     </row>
@@ -86489,15 +86208,9 @@
         <v>6</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>345172.27</v>
       </c>
       <c r="G90">
-        <v>1</v>
-      </c>
-      <c r="H90">
-        <v>345172.27</v>
-      </c>
-      <c r="I90">
         <v>0.113331599930837</v>
       </c>
     </row>
@@ -86520,15 +86233,9 @@
         <v>6</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>239708.08</v>
       </c>
       <c r="G91">
-        <v>1</v>
-      </c>
-      <c r="H91">
-        <v>239708.08</v>
-      </c>
-      <c r="I91">
         <v>0.2561092860454482</v>
       </c>
     </row>
@@ -86551,15 +86258,9 @@
         <v>6</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>314694.34</v>
       </c>
       <c r="G92">
-        <v>1</v>
-      </c>
-      <c r="H92">
-        <v>314694.34</v>
-      </c>
-      <c r="I92">
         <v>0.1684034724572833</v>
       </c>
     </row>
@@ -86582,15 +86283,9 @@
         <v>6</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>378107.24</v>
       </c>
       <c r="G93">
-        <v>1</v>
-      </c>
-      <c r="H93">
-        <v>378107.24</v>
-      </c>
-      <c r="I93">
         <v>0.09315409449775935</v>
       </c>
     </row>
@@ -86613,15 +86308,9 @@
         <v>6</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>313074.69</v>
       </c>
       <c r="G94">
-        <v>1</v>
-      </c>
-      <c r="H94">
-        <v>313074.69</v>
-      </c>
-      <c r="I94">
         <v>0.09434189477192394</v>
       </c>
     </row>
@@ -86644,15 +86333,9 @@
         <v>6</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>498040.73</v>
       </c>
       <c r="G95">
-        <v>1</v>
-      </c>
-      <c r="H95">
-        <v>498040.73</v>
-      </c>
-      <c r="I95">
         <v>0.08643153398305017</v>
       </c>
     </row>
@@ -86675,15 +86358,9 @@
         <v>6</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>519129.48</v>
       </c>
       <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>519129.48</v>
-      </c>
-      <c r="I96">
         <v>0.07369772794181051</v>
       </c>
     </row>
@@ -86706,15 +86383,9 @@
         <v>6</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>662711.85</v>
       </c>
       <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97">
-        <v>662711.85</v>
-      </c>
-      <c r="I97">
         <v>0.07135212383059486</v>
       </c>
     </row>
@@ -86737,15 +86408,9 @@
         <v>6</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>608054.85</v>
       </c>
       <c r="G98">
-        <v>1</v>
-      </c>
-      <c r="H98">
-        <v>608054.85</v>
-      </c>
-      <c r="I98">
         <v>0.07647685266201489</v>
       </c>
     </row>
@@ -86768,15 +86433,9 @@
         <v>6</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>482358.76</v>
       </c>
       <c r="G99">
-        <v>1</v>
-      </c>
-      <c r="H99">
-        <v>482358.76</v>
-      </c>
-      <c r="I99">
         <v>0.07789075147723032</v>
       </c>
     </row>
@@ -86799,15 +86458,9 @@
         <v>6</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>530126.8</v>
       </c>
       <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100">
-        <v>530126.8</v>
-      </c>
-      <c r="I100">
         <v>0.08653101992209057</v>
       </c>
     </row>
@@ -86830,15 +86483,9 @@
         <v>6</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>406854.55</v>
       </c>
       <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>406854.55</v>
-      </c>
-      <c r="I101">
         <v>0.09920320457115754</v>
       </c>
     </row>
@@ -86861,15 +86508,9 @@
         <v>6</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>528666.9399999999</v>
       </c>
       <c r="G102">
-        <v>1</v>
-      </c>
-      <c r="H102">
-        <v>528666.9399999999</v>
-      </c>
-      <c r="I102">
         <v>0.0832323693709324</v>
       </c>
     </row>
@@ -86892,15 +86533,9 @@
         <v>6</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>522105.7</v>
       </c>
       <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>522105.7</v>
-      </c>
-      <c r="I103">
         <v>0.07684546681090779</v>
       </c>
     </row>
@@ -86923,15 +86558,9 @@
         <v>6</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>402886.53</v>
       </c>
       <c r="G104">
-        <v>1</v>
-      </c>
-      <c r="H104">
-        <v>402886.53</v>
-      </c>
-      <c r="I104">
         <v>0.1067854365694039</v>
       </c>
     </row>
@@ -86954,15 +86583,9 @@
         <v>6</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>405508.71</v>
       </c>
       <c r="G105">
-        <v>1</v>
-      </c>
-      <c r="H105">
-        <v>405508.71</v>
-      </c>
-      <c r="I105">
         <v>0.0886620178671812</v>
       </c>
     </row>
@@ -86985,15 +86608,9 @@
         <v>6</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>465616.03</v>
       </c>
       <c r="G106">
-        <v>1</v>
-      </c>
-      <c r="H106">
-        <v>465616.03</v>
-      </c>
-      <c r="I106">
         <v>0.06919091547755293</v>
       </c>
     </row>
@@ -87016,15 +86633,9 @@
         <v>6</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>409243.1</v>
       </c>
       <c r="G107">
-        <v>1</v>
-      </c>
-      <c r="H107">
-        <v>409243.1</v>
-      </c>
-      <c r="I107">
         <v>0.06153854294100232</v>
       </c>
     </row>
@@ -87047,15 +86658,9 @@
         <v>6</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>475263.58</v>
       </c>
       <c r="G108">
-        <v>1</v>
-      </c>
-      <c r="H108">
-        <v>475263.58</v>
-      </c>
-      <c r="I108">
         <v>0.04844514111459635</v>
       </c>
     </row>
@@ -87078,15 +86683,9 @@
         <v>6</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>424194.01</v>
       </c>
       <c r="G109">
-        <v>1</v>
-      </c>
-      <c r="H109">
-        <v>424194.01</v>
-      </c>
-      <c r="I109">
         <v>0.06539156627912811</v>
       </c>
     </row>
@@ -87109,15 +86708,9 @@
         <v>6</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>7460</v>
       </c>
       <c r="G110">
-        <v>1</v>
-      </c>
-      <c r="H110">
-        <v>7460</v>
-      </c>
-      <c r="I110">
         <v>0.2</v>
       </c>
     </row>
@@ -87140,15 +86733,9 @@
         <v>6</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>4900</v>
       </c>
       <c r="G111">
-        <v>1</v>
-      </c>
-      <c r="H111">
-        <v>4900</v>
-      </c>
-      <c r="I111">
         <v>0.2</v>
       </c>
     </row>
@@ -87171,15 +86758,9 @@
         <v>6</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>4800</v>
       </c>
       <c r="G112">
-        <v>1</v>
-      </c>
-      <c r="H112">
-        <v>4800</v>
-      </c>
-      <c r="I112">
         <v>0.2</v>
       </c>
     </row>
@@ -87202,15 +86783,9 @@
         <v>6</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>4680</v>
       </c>
       <c r="G113">
-        <v>1</v>
-      </c>
-      <c r="H113">
-        <v>4680</v>
-      </c>
-      <c r="I113">
         <v>0.2</v>
       </c>
     </row>
@@ -87233,15 +86808,9 @@
         <v>6</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>1450</v>
       </c>
       <c r="G114">
-        <v>1</v>
-      </c>
-      <c r="H114">
-        <v>1450</v>
-      </c>
-      <c r="I114">
         <v>0.2</v>
       </c>
     </row>
@@ -87264,15 +86833,9 @@
         <v>6</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>2886.228</v>
       </c>
       <c r="G115">
-        <v>1</v>
-      </c>
-      <c r="H115">
-        <v>2886.228</v>
-      </c>
-      <c r="I115">
         <v>0.2</v>
       </c>
     </row>
@@ -87295,15 +86858,9 @@
         <v>6</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>2310.729</v>
       </c>
       <c r="G116">
-        <v>1</v>
-      </c>
-      <c r="H116">
-        <v>2310.729</v>
-      </c>
-      <c r="I116">
         <v>0.2</v>
       </c>
     </row>
@@ -87326,15 +86883,9 @@
         <v>6</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>2592.182</v>
       </c>
       <c r="G117">
-        <v>1</v>
-      </c>
-      <c r="H117">
-        <v>2592.182</v>
-      </c>
-      <c r="I117">
         <v>0.2</v>
       </c>
     </row>
@@ -87357,15 +86908,9 @@
         <v>6</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>3285.079</v>
       </c>
       <c r="G118">
-        <v>1</v>
-      </c>
-      <c r="H118">
-        <v>3285.079</v>
-      </c>
-      <c r="I118">
         <v>0.2</v>
       </c>
     </row>
@@ -87388,15 +86933,9 @@
         <v>6</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>3048.697</v>
       </c>
       <c r="G119">
-        <v>1</v>
-      </c>
-      <c r="H119">
-        <v>3048.697</v>
-      </c>
-      <c r="I119">
         <v>0.2</v>
       </c>
     </row>
@@ -87419,15 +86958,9 @@
         <v>6</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>3621.817</v>
       </c>
       <c r="G120">
-        <v>1</v>
-      </c>
-      <c r="H120">
-        <v>3621.817</v>
-      </c>
-      <c r="I120">
         <v>0.2</v>
       </c>
     </row>
@@ -87450,15 +86983,9 @@
         <v>6</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>3306.936964</v>
       </c>
       <c r="G121">
-        <v>1</v>
-      </c>
-      <c r="H121">
-        <v>3306.936964</v>
-      </c>
-      <c r="I121">
         <v>0.2</v>
       </c>
     </row>
@@ -87481,15 +87008,9 @@
         <v>6</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>1560.134118</v>
       </c>
       <c r="G122">
-        <v>1</v>
-      </c>
-      <c r="H122">
-        <v>1560.134118</v>
-      </c>
-      <c r="I122">
         <v>0.2</v>
       </c>
     </row>
@@ -87512,15 +87033,9 @@
         <v>6</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>1769.018516</v>
       </c>
       <c r="G123">
-        <v>1</v>
-      </c>
-      <c r="H123">
-        <v>1769.018516</v>
-      </c>
-      <c r="I123">
         <v>0.2</v>
       </c>
     </row>
@@ -87543,15 +87058,9 @@
         <v>6</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>996.9392679</v>
       </c>
       <c r="G124">
-        <v>1</v>
-      </c>
-      <c r="H124">
-        <v>996.9392679</v>
-      </c>
-      <c r="I124">
         <v>0.2</v>
       </c>
     </row>
@@ -87574,15 +87083,9 @@
         <v>6</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>923.8433659999999</v>
       </c>
       <c r="G125">
-        <v>1</v>
-      </c>
-      <c r="H125">
-        <v>923.8433659999999</v>
-      </c>
-      <c r="I125">
         <v>0.2</v>
       </c>
     </row>
@@ -87605,15 +87108,9 @@
         <v>6</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>2322.642938</v>
       </c>
       <c r="G126">
-        <v>1</v>
-      </c>
-      <c r="H126">
-        <v>2322.642938</v>
-      </c>
-      <c r="I126">
         <v>0.2</v>
       </c>
     </row>
@@ -87636,15 +87133,9 @@
         <v>6</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>1842.79206</v>
       </c>
       <c r="G127">
-        <v>1</v>
-      </c>
-      <c r="H127">
-        <v>1842.79206</v>
-      </c>
-      <c r="I127">
         <v>0.2</v>
       </c>
     </row>
@@ -87667,15 +87158,9 @@
         <v>6</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>3501.938121</v>
       </c>
       <c r="G128">
-        <v>1</v>
-      </c>
-      <c r="H128">
-        <v>3501.938121</v>
-      </c>
-      <c r="I128">
         <v>0.2</v>
       </c>
     </row>
@@ -87698,15 +87183,9 @@
         <v>6</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>4828.889687</v>
       </c>
       <c r="G129">
-        <v>1</v>
-      </c>
-      <c r="H129">
-        <v>4828.889687</v>
-      </c>
-      <c r="I129">
         <v>0.2</v>
       </c>
     </row>
@@ -87717,7 +87196,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -87748,15 +87227,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Selectivity_block</t>
+          <t>Catch</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Catch</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Log_sd</t>
         </is>
@@ -87781,12 +87255,9 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>935714</v>
       </c>
       <c r="G2">
-        <v>935714</v>
-      </c>
-      <c r="H2">
         <v>0.05</v>
       </c>
     </row>
@@ -87809,12 +87280,9 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>958280</v>
       </c>
       <c r="G3">
-        <v>958280</v>
-      </c>
-      <c r="H3">
         <v>0.05</v>
       </c>
     </row>
@@ -87837,12 +87305,9 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>973502</v>
       </c>
       <c r="G4">
-        <v>973502</v>
-      </c>
-      <c r="H4">
         <v>0.05</v>
       </c>
     </row>
@@ -87865,12 +87330,9 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>955964</v>
       </c>
       <c r="G5">
-        <v>955964</v>
-      </c>
-      <c r="H5">
         <v>0.05</v>
       </c>
     </row>
@@ -87893,12 +87355,9 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>981450</v>
       </c>
       <c r="G6">
-        <v>981450</v>
-      </c>
-      <c r="H6">
         <v>0.05</v>
       </c>
     </row>
@@ -87921,12 +87380,9 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>1092055</v>
       </c>
       <c r="G7">
-        <v>1092055</v>
-      </c>
-      <c r="H7">
         <v>0.05</v>
       </c>
     </row>
@@ -87949,12 +87405,9 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>1139676</v>
       </c>
       <c r="G8">
-        <v>1139676</v>
-      </c>
-      <c r="H8">
         <v>0.05</v>
       </c>
     </row>
@@ -87977,12 +87430,9 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>1141993</v>
       </c>
       <c r="G9">
-        <v>1141993</v>
-      </c>
-      <c r="H9">
         <v>0.05</v>
       </c>
     </row>
@@ -88005,12 +87455,9 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>859416</v>
       </c>
       <c r="G10">
-        <v>859416</v>
-      </c>
-      <c r="H10">
         <v>0.05</v>
       </c>
     </row>
@@ -88033,12 +87480,9 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>1228721</v>
       </c>
       <c r="G11">
-        <v>1228721</v>
-      </c>
-      <c r="H11">
         <v>0.05</v>
       </c>
     </row>
@@ -88061,12 +87505,9 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>1229600</v>
       </c>
       <c r="G12">
-        <v>1229600</v>
-      </c>
-      <c r="H12">
         <v>0.05</v>
       </c>
     </row>
@@ -88089,12 +87530,9 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>1455193</v>
       </c>
       <c r="G13">
-        <v>1455193</v>
-      </c>
-      <c r="H13">
         <v>0.05</v>
       </c>
     </row>
@@ -88117,12 +87555,9 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>1195608.279</v>
       </c>
       <c r="G14">
-        <v>1195608.279</v>
-      </c>
-      <c r="H14">
         <v>0.05</v>
       </c>
     </row>
@@ -88145,12 +87580,9 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>1390330.91</v>
       </c>
       <c r="G15">
-        <v>1390330.91</v>
-      </c>
-      <c r="H15">
         <v>0.05</v>
       </c>
     </row>
@@ -88173,12 +87605,9 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>1326600.66</v>
       </c>
       <c r="G16">
-        <v>1326600.66</v>
-      </c>
-      <c r="H16">
         <v>0.05</v>
       </c>
     </row>
@@ -88201,12 +87630,9 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>1329349.87</v>
       </c>
       <c r="G17">
-        <v>1329349.87</v>
-      </c>
-      <c r="H17">
         <v>0.05</v>
       </c>
     </row>
@@ -88229,12 +87655,9 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>1264244.54</v>
       </c>
       <c r="G18">
-        <v>1264244.54</v>
-      </c>
-      <c r="H18">
         <v>0.05</v>
       </c>
     </row>
@@ -88257,12 +87680,9 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>1192778.411</v>
       </c>
       <c r="G19">
-        <v>1192778.411</v>
-      </c>
-      <c r="H19">
         <v>0.05</v>
       </c>
     </row>
@@ -88285,12 +87705,9 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>1124430.415</v>
       </c>
       <c r="G20">
-        <v>1124430.415</v>
-      </c>
-      <c r="H20">
         <v>0.05</v>
       </c>
     </row>
@@ -88313,12 +87730,9 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>1101165.453</v>
       </c>
       <c r="G21">
-        <v>1101165.453</v>
-      </c>
-      <c r="H21">
         <v>0.05</v>
       </c>
     </row>
@@ -88341,12 +87755,9 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>989815.914</v>
       </c>
       <c r="G22">
-        <v>989815.914</v>
-      </c>
-      <c r="H22">
         <v>0.05</v>
       </c>
     </row>
@@ -88369,12 +87780,9 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>1132707.038</v>
       </c>
       <c r="G23">
-        <v>1132707.038</v>
-      </c>
-      <c r="H23">
         <v>0.05</v>
       </c>
     </row>
@@ -88397,12 +87805,9 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>1387193.651</v>
       </c>
       <c r="G24">
-        <v>1387193.651</v>
-      </c>
-      <c r="H24">
         <v>0.05</v>
       </c>
     </row>
@@ -88425,12 +87830,9 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>1480192.723</v>
       </c>
       <c r="G25">
-        <v>1480192.723</v>
-      </c>
-      <c r="H25">
         <v>0.05</v>
       </c>
     </row>
@@ -88453,12 +87855,9 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>1490899.096</v>
       </c>
       <c r="G26">
-        <v>1490899.096</v>
-      </c>
-      <c r="H26">
         <v>0.05</v>
       </c>
     </row>
@@ -88481,12 +87880,9 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>1480542.528</v>
       </c>
       <c r="G27">
-        <v>1480542.528</v>
-      </c>
-      <c r="H27">
         <v>0.05</v>
       </c>
     </row>
@@ -88509,12 +87905,9 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>1483285.763</v>
       </c>
       <c r="G28">
-        <v>1483285.763</v>
-      </c>
-      <c r="H28">
         <v>0.05</v>
       </c>
     </row>
@@ -88537,12 +87930,9 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>1486435.323</v>
       </c>
       <c r="G29">
-        <v>1486435.323</v>
-      </c>
-      <c r="H29">
         <v>0.05</v>
       </c>
     </row>
@@ -88565,12 +87955,9 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>1354097.161</v>
       </c>
       <c r="G30">
-        <v>1354097.161</v>
-      </c>
-      <c r="H30">
         <v>0.05</v>
       </c>
     </row>
@@ -88593,12 +87980,9 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>990565.64</v>
       </c>
       <c r="G31">
-        <v>990565.64</v>
-      </c>
-      <c r="H31">
         <v>0.05</v>
       </c>
     </row>
@@ -88621,12 +88005,9 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>807946.6090000001</v>
       </c>
       <c r="G32">
-        <v>807946.6090000001</v>
-      </c>
-      <c r="H32">
         <v>0.05</v>
       </c>
     </row>
@@ -88649,12 +88030,9 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>810215.206</v>
       </c>
       <c r="G33">
-        <v>810215.206</v>
-      </c>
-      <c r="H33">
         <v>0.05</v>
       </c>
     </row>
@@ -88677,12 +88055,9 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>1199213.635</v>
       </c>
       <c r="G34">
-        <v>1199213.635</v>
-      </c>
-      <c r="H34">
         <v>0.05</v>
       </c>
     </row>
@@ -88705,12 +88080,9 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>1205283.061</v>
       </c>
       <c r="G35">
-        <v>1205283.061</v>
-      </c>
-      <c r="H35">
         <v>0.05</v>
       </c>
     </row>
@@ -88733,12 +88105,9 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>1270824.308</v>
       </c>
       <c r="G36">
-        <v>1270824.308</v>
-      </c>
-      <c r="H36">
         <v>0.05</v>
       </c>
     </row>
@@ -88761,12 +88130,9 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>1297846.257</v>
       </c>
       <c r="G37">
-        <v>1297846.257</v>
-      </c>
-      <c r="H37">
         <v>0.05</v>
       </c>
     </row>
@@ -88789,12 +88155,9 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>1322311.572</v>
       </c>
       <c r="G38">
-        <v>1322311.572</v>
-      </c>
-      <c r="H38">
         <v>0.05</v>
       </c>
     </row>
@@ -88817,12 +88180,9 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>1343465.851</v>
       </c>
       <c r="G39">
-        <v>1343465.851</v>
-      </c>
-      <c r="H39">
         <v>0.05</v>
       </c>
     </row>
@@ -88845,12 +88205,9 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>1343465.851</v>
       </c>
       <c r="G40">
-        <v>1343465.851</v>
-      </c>
-      <c r="H40">
         <v>0.05</v>
       </c>
     </row>
@@ -88873,12 +88230,9 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>36004</v>
       </c>
       <c r="G41">
-        <v>36004</v>
-      </c>
-      <c r="H41">
         <v>0.05</v>
       </c>
     </row>
@@ -88901,12 +88255,9 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>41042</v>
       </c>
       <c r="G42">
-        <v>41042</v>
-      </c>
-      <c r="H42">
         <v>0.05</v>
       </c>
     </row>
@@ -88929,12 +88280,9 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>56492</v>
       </c>
       <c r="G43">
-        <v>56492</v>
-      </c>
-      <c r="H43">
         <v>0.05</v>
       </c>
     </row>
@@ -88957,12 +88305,9 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>59386</v>
       </c>
       <c r="G44">
-        <v>59386</v>
-      </c>
-      <c r="H44">
         <v>0.05</v>
       </c>
     </row>
@@ -88985,12 +88330,9 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>94207</v>
       </c>
       <c r="G45">
-        <v>94207</v>
-      </c>
-      <c r="H45">
         <v>0.05</v>
       </c>
     </row>
@@ -89013,12 +88355,9 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>124895</v>
       </c>
       <c r="G46">
-        <v>124895</v>
-      </c>
-      <c r="H46">
         <v>0.05</v>
       </c>
     </row>
@@ -89041,12 +88380,9 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>143449</v>
       </c>
       <c r="G47">
-        <v>143449</v>
-      </c>
-      <c r="H47">
         <v>0.05</v>
       </c>
     </row>
@@ -89069,12 +88405,9 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>135376</v>
       </c>
       <c r="G48">
-        <v>135376</v>
-      </c>
-      <c r="H48">
         <v>0.05</v>
       </c>
     </row>
@@ -89097,12 +88430,9 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>149900</v>
       </c>
       <c r="G49">
-        <v>149900</v>
-      </c>
-      <c r="H49">
         <v>0.05</v>
       </c>
     </row>
@@ -89125,12 +88455,9 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>203075</v>
       </c>
       <c r="G50">
-        <v>203075</v>
-      </c>
-      <c r="H50">
         <v>0.05</v>
       </c>
     </row>
@@ -89153,12 +88480,9 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>178326</v>
       </c>
       <c r="G51">
-        <v>178326</v>
-      </c>
-      <c r="H51">
         <v>0.05</v>
       </c>
     </row>
@@ -89181,12 +88505,9 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>172065</v>
       </c>
       <c r="G52">
-        <v>172065</v>
-      </c>
-      <c r="H52">
         <v>0.05</v>
       </c>
     </row>
@@ -89209,12 +88530,9 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>210242</v>
       </c>
       <c r="G53">
-        <v>210242</v>
-      </c>
-      <c r="H53">
         <v>0.05</v>
       </c>
     </row>
@@ -89237,12 +88555,9 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>164210</v>
       </c>
       <c r="G54">
-        <v>164210</v>
-      </c>
-      <c r="H54">
         <v>0.05</v>
       </c>
     </row>
@@ -89265,12 +88580,9 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>133186</v>
       </c>
       <c r="G55">
-        <v>133186</v>
-      </c>
-      <c r="H55">
         <v>0.05</v>
       </c>
     </row>
@@ -89293,12 +88605,9 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>172263</v>
       </c>
       <c r="G56">
-        <v>172263</v>
-      </c>
-      <c r="H56">
         <v>0.05</v>
       </c>
     </row>
@@ -89321,12 +88630,9 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>228499</v>
       </c>
       <c r="G57">
-        <v>228499</v>
-      </c>
-      <c r="H57">
         <v>0.05</v>
       </c>
     </row>
@@ -89349,12 +88655,9 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>209065</v>
       </c>
       <c r="G58">
-        <v>209065</v>
-      </c>
-      <c r="H58">
         <v>0.05</v>
       </c>
     </row>
@@ -89377,12 +88680,9 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>232600</v>
       </c>
       <c r="G59">
-        <v>232600</v>
-      </c>
-      <c r="H59">
         <v>0.05</v>
       </c>
     </row>
@@ -89405,12 +88705,9 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>158529</v>
       </c>
       <c r="G60">
-        <v>158529</v>
-      </c>
-      <c r="H60">
         <v>0.05</v>
       </c>
     </row>
@@ -89433,12 +88730,9 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>145867</v>
       </c>
       <c r="G61">
-        <v>145867</v>
-      </c>
-      <c r="H61">
         <v>0.05</v>
       </c>
     </row>
@@ -89461,12 +88755,9 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>151378</v>
       </c>
       <c r="G62">
-        <v>151378</v>
-      </c>
-      <c r="H62">
         <v>0.05</v>
       </c>
     </row>
@@ -89489,12 +88780,9 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>142542</v>
       </c>
       <c r="G63">
-        <v>142542</v>
-      </c>
-      <c r="H63">
         <v>0.05</v>
       </c>
     </row>
@@ -89517,12 +88805,9 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>166556</v>
       </c>
       <c r="G64">
-        <v>166556</v>
-      </c>
-      <c r="H64">
         <v>0.05</v>
       </c>
     </row>
@@ -89545,12 +88830,9 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>175437</v>
       </c>
       <c r="G65">
-        <v>175437</v>
-      </c>
-      <c r="H65">
         <v>0.05</v>
       </c>
     </row>
@@ -89573,12 +88855,9 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>183749</v>
       </c>
       <c r="G66">
-        <v>183749</v>
-      </c>
-      <c r="H66">
         <v>0.05</v>
       </c>
     </row>
@@ -89601,12 +88880,9 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>182942</v>
       </c>
       <c r="G67">
-        <v>182942</v>
-      </c>
-      <c r="H67">
         <v>0.05</v>
       </c>
     </row>
@@ -89629,12 +88905,9 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>168818</v>
       </c>
       <c r="G68">
-        <v>168818</v>
-      </c>
-      <c r="H68">
         <v>0.05</v>
       </c>
     </row>
@@ -89657,12 +88930,9 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>140127</v>
       </c>
       <c r="G69">
-        <v>140127</v>
-      </c>
-      <c r="H69">
         <v>0.05</v>
       </c>
     </row>
@@ -89685,12 +88955,9 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>139803</v>
       </c>
       <c r="G70">
-        <v>139803</v>
-      </c>
-      <c r="H70">
         <v>0.05</v>
       </c>
     </row>
@@ -89713,12 +88980,9 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>147174</v>
       </c>
       <c r="G71">
-        <v>147174</v>
-      </c>
-      <c r="H71">
         <v>0.05</v>
       </c>
     </row>
@@ -89741,12 +89005,9 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>142868</v>
       </c>
       <c r="G72">
-        <v>142868</v>
-      </c>
-      <c r="H72">
         <v>0.05</v>
       </c>
     </row>
@@ -89769,12 +89030,9 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>209214.653</v>
       </c>
       <c r="G73">
-        <v>209214.653</v>
-      </c>
-      <c r="H73">
         <v>0.05</v>
       </c>
     </row>
@@ -89797,12 +89055,9 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>232784.286</v>
       </c>
       <c r="G74">
-        <v>232784.286</v>
-      </c>
-      <c r="H74">
         <v>0.05</v>
       </c>
     </row>
@@ -89825,12 +89080,9 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>236690.77</v>
       </c>
       <c r="G75">
-        <v>236690.77</v>
-      </c>
-      <c r="H75">
         <v>0.05</v>
       </c>
     </row>
@@ -89853,12 +89105,9 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>238763.29</v>
       </c>
       <c r="G76">
-        <v>238763.29</v>
-      </c>
-      <c r="H76">
         <v>0.05</v>
       </c>
     </row>
@@ -89881,12 +89130,9 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>232832.084</v>
       </c>
       <c r="G77">
-        <v>232832.084</v>
-      </c>
-      <c r="H77">
         <v>0.05</v>
       </c>
     </row>
@@ -89909,12 +89155,9 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>215513.651</v>
       </c>
       <c r="G78">
-        <v>215513.651</v>
-      </c>
-      <c r="H78">
         <v>0.05</v>
       </c>
     </row>
@@ -89937,12 +89180,9 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>215513.651</v>
       </c>
       <c r="G79">
-        <v>215513.651</v>
-      </c>
-      <c r="H79">
         <v>0.05</v>
       </c>
     </row>
@@ -89965,12 +89205,9 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>13352</v>
       </c>
       <c r="G80">
-        <v>13352</v>
-      </c>
-      <c r="H80">
         <v>0.05</v>
       </c>
     </row>
@@ -89993,12 +89230,9 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>17079</v>
       </c>
       <c r="G81">
-        <v>17079</v>
-      </c>
-      <c r="H81">
         <v>0.05</v>
       </c>
     </row>
@@ -90021,12 +89255,9 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>15915</v>
       </c>
       <c r="G82">
-        <v>15915</v>
-      </c>
-      <c r="H82">
         <v>0.05</v>
       </c>
     </row>
@@ -90049,12 +89280,9 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>10712</v>
       </c>
       <c r="G83">
-        <v>10712</v>
-      </c>
-      <c r="H83">
         <v>0.05</v>
       </c>
     </row>
@@ -90077,12 +89305,9 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>12991</v>
       </c>
       <c r="G84">
-        <v>12991</v>
-      </c>
-      <c r="H84">
         <v>0.05</v>
       </c>
     </row>
@@ -90105,12 +89330,9 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>8790</v>
       </c>
       <c r="G85">
-        <v>8790</v>
-      </c>
-      <c r="H85">
         <v>0.05</v>
       </c>
     </row>
@@ -90133,12 +89355,9 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>6926</v>
       </c>
       <c r="G86">
-        <v>6926</v>
-      </c>
-      <c r="H86">
         <v>0.05</v>
       </c>
     </row>
@@ -90161,12 +89380,9 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>6678</v>
       </c>
       <c r="G87">
-        <v>6678</v>
-      </c>
-      <c r="H87">
         <v>0.05</v>
       </c>
     </row>
@@ -90189,12 +89405,9 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>4519</v>
       </c>
       <c r="G88">
-        <v>4519</v>
-      </c>
-      <c r="H88">
         <v>0.05</v>
       </c>
     </row>
@@ -90217,12 +89430,9 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>18591</v>
       </c>
       <c r="G89">
-        <v>18591</v>
-      </c>
-      <c r="H89">
         <v>0.05</v>
       </c>
     </row>
@@ -90245,12 +89455,9 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>6795</v>
       </c>
       <c r="G90">
-        <v>6795</v>
-      </c>
-      <c r="H90">
         <v>0.05</v>
       </c>
     </row>
@@ -90273,12 +89480,9 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>12144</v>
       </c>
       <c r="G91">
-        <v>12144</v>
-      </c>
-      <c r="H91">
         <v>0.05</v>
       </c>
     </row>
@@ -90301,12 +89505,9 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>17834.85</v>
       </c>
       <c r="G92">
-        <v>17834.85</v>
-      </c>
-      <c r="H92">
         <v>0.05</v>
       </c>
     </row>
@@ -90329,12 +89530,9 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>10949.88</v>
       </c>
       <c r="G93">
-        <v>10949.88</v>
-      </c>
-      <c r="H93">
         <v>0.05</v>
       </c>
     </row>
@@ -90357,12 +89555,9 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>7952.92</v>
       </c>
       <c r="G94">
-        <v>7952.92</v>
-      </c>
-      <c r="H94">
         <v>0.05</v>
       </c>
     </row>
@@ -90385,12 +89580,9 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>13017.95</v>
       </c>
       <c r="G95">
-        <v>13017.95</v>
-      </c>
-      <c r="H95">
         <v>0.05</v>
       </c>
     </row>
@@ -90413,12 +89605,9 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>8282.93</v>
       </c>
       <c r="G96">
-        <v>8282.93</v>
-      </c>
-      <c r="H96">
         <v>0.05</v>
       </c>
     </row>
@@ -90441,12 +89630,9 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>13308.83</v>
       </c>
       <c r="G97">
-        <v>13308.83</v>
-      </c>
-      <c r="H97">
         <v>0.05</v>
       </c>
     </row>
@@ -90469,12 +89655,9 @@
         <v>0</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>9228.52</v>
       </c>
       <c r="G98">
-        <v>9228.52</v>
-      </c>
-      <c r="H98">
         <v>0.05</v>
       </c>
     </row>
@@ -90497,12 +89680,9 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>14595.56</v>
       </c>
       <c r="G99">
-        <v>14595.56</v>
-      </c>
-      <c r="H99">
         <v>0.05</v>
       </c>
     </row>
@@ -90525,12 +89705,9 @@
         <v>0</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>10595.79</v>
       </c>
       <c r="G100">
-        <v>10595.79</v>
-      </c>
-      <c r="H100">
         <v>0.05</v>
       </c>
     </row>
@@ -90553,12 +89730,9 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>12072.65</v>
       </c>
       <c r="G101">
-        <v>12072.65</v>
-      </c>
-      <c r="H101">
         <v>0.05</v>
       </c>
     </row>
@@ -90581,12 +89755,9 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>12837.82</v>
       </c>
       <c r="G102">
-        <v>12837.82</v>
-      </c>
-      <c r="H102">
         <v>0.05</v>
       </c>
     </row>
@@ -90609,12 +89780,9 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>10822.71</v>
       </c>
       <c r="G103">
-        <v>10822.71</v>
-      </c>
-      <c r="H103">
         <v>0.05</v>
       </c>
     </row>
@@ -90637,12 +89805,9 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>12278.492</v>
       </c>
       <c r="G104">
-        <v>12278.492</v>
-      </c>
-      <c r="H104">
         <v>0.05</v>
       </c>
     </row>
@@ -90665,12 +89830,9 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>17365.168</v>
       </c>
       <c r="G105">
-        <v>17365.168</v>
-      </c>
-      <c r="H105">
         <v>0.05</v>
       </c>
     </row>
@@ -90693,12 +89855,9 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>13408.722</v>
       </c>
       <c r="G106">
-        <v>13408.722</v>
-      </c>
-      <c r="H106">
         <v>0.05</v>
       </c>
     </row>
@@ -90721,12 +89880,9 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>11966.769</v>
       </c>
       <c r="G107">
-        <v>11966.769</v>
-      </c>
-      <c r="H107">
         <v>0.05</v>
       </c>
     </row>
@@ -90749,12 +89905,9 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>11081.715</v>
       </c>
       <c r="G108">
-        <v>11081.715</v>
-      </c>
-      <c r="H108">
         <v>0.05</v>
       </c>
     </row>
@@ -90777,12 +89930,9 @@
         <v>0</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>18897.328</v>
       </c>
       <c r="G109">
-        <v>18897.328</v>
-      </c>
-      <c r="H109">
         <v>0.05</v>
       </c>
     </row>
@@ -90805,12 +89955,9 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>19212.001</v>
       </c>
       <c r="G110">
-        <v>19212.001</v>
-      </c>
-      <c r="H110">
         <v>0.05</v>
       </c>
     </row>
@@ -90833,12 +89980,9 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>14751.644</v>
       </c>
       <c r="G111">
-        <v>14751.644</v>
-      </c>
-      <c r="H111">
         <v>0.05</v>
       </c>
     </row>
@@ -90861,12 +90005,9 @@
         <v>0</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>16840.734</v>
       </c>
       <c r="G112">
-        <v>16840.734</v>
-      </c>
-      <c r="H112">
         <v>0.05</v>
       </c>
     </row>
@@ -90889,12 +90030,9 @@
         <v>0</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>18940.722</v>
       </c>
       <c r="G113">
-        <v>18940.722</v>
-      </c>
-      <c r="H113">
         <v>0.05</v>
       </c>
     </row>
@@ -90917,12 +90055,9 @@
         <v>0</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>14054.765</v>
       </c>
       <c r="G114">
-        <v>14054.765</v>
-      </c>
-      <c r="H114">
         <v>0.05</v>
       </c>
     </row>
@@ -90945,12 +90080,9 @@
         <v>0</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>14923.544</v>
       </c>
       <c r="G115">
-        <v>14923.544</v>
-      </c>
-      <c r="H115">
         <v>0.05</v>
       </c>
     </row>
@@ -90973,12 +90105,9 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>10329.709</v>
       </c>
       <c r="G116">
-        <v>10329.709</v>
-      </c>
-      <c r="H116">
         <v>0.05</v>
       </c>
     </row>
@@ -91001,12 +90130,9 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>13102.67267</v>
       </c>
       <c r="G117">
-        <v>13102.67267</v>
-      </c>
-      <c r="H117">
         <v>0.05</v>
       </c>
     </row>
@@ -91029,12 +90155,9 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>13102.67267</v>
       </c>
       <c r="G118">
-        <v>13102.67267</v>
-      </c>
-      <c r="H118">
         <v>0.05</v>
       </c>
     </row>
